--- a/docs/oc-mensuales/gas-licuado-de-petroleo/nov-2025.xlsx
+++ b/docs/oc-mensuales/gas-licuado-de-petroleo/nov-2025.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>83.56</v>
+        <v>82.84999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>443.19</v>
+        <v>439.44</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>9290.98</v>
+        <v>9212.290000000001</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1094.82</v>
+        <v>1085.55</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>236.7</v>
+        <v>234.7</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>387.49</v>
+        <v>384.2</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>173.98</v>
+        <v>172.51</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>474.82</v>
+        <v>470.8</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3447.56</v>
+        <v>3418.36</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1142.06</v>
+        <v>1132.38</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1699.35</v>
+        <v>1684.96</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1699.35</v>
+        <v>1684.96</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>228.41</v>
+        <v>226.48</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>434.95</v>
+        <v>431.26</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3989.55</v>
+        <v>3955.76</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>55.18</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1365.89</v>
+        <v>1354.32</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1958.54</v>
+        <v>1941.95</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>221.59</v>
+        <v>219.72</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1022.51</v>
+        <v>1013.85</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>4731.02</v>
+        <v>4690.95</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>134.64</v>
+        <v>133.5</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1185.93</v>
+        <v>1175.89</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>399.85</v>
+        <v>396.46</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>174.41</v>
+        <v>172.94</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>699.73</v>
+        <v>693.8099999999999</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2199.71</v>
+        <v>2181.08</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>125.52</v>
+        <v>124.46</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>179.58</v>
+        <v>178.05</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>9094.110000000001</v>
+        <v>9017.09</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>4427.89</v>
+        <v>4390.39</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>241.83</v>
+        <v>239.78</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>391.45</v>
+        <v>388.14</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>258.74</v>
+        <v>256.55</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2647.84</v>
+        <v>2625.42</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>722.12</v>
+        <v>716</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>339.18</v>
+        <v>336.31</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1120.18</v>
+        <v>1110.7</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>191.78</v>
+        <v>190.16</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1070.55</v>
+        <v>1061.48</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1157.21</v>
+        <v>1147.41</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2014.5</v>
+        <v>1997.44</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>85.84999999999999</v>
+        <v>85.12</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1175.12</v>
+        <v>1165.17</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>6485.43</v>
+        <v>6430.51</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2510.49</v>
+        <v>2489.23</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>836.83</v>
+        <v>829.74</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>4686.5</v>
+        <v>4646.81</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>894.7</v>
+        <v>887.12</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>130.48</v>
+        <v>129.38</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>537.96</v>
+        <v>533.41</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>208.06</v>
+        <v>206.3</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3984.23</v>
+        <v>3963.76</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>792.95</v>
+        <v>788.88</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2087.26</v>
+        <v>2076.53</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>329.64</v>
+        <v>327.95</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>4798.08</v>
+        <v>4773.43</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1328.25</v>
+        <v>1321.42</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>83.02</v>
+        <v>82.59</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1246.6</v>
+        <v>1240.19</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>9006.02</v>
+        <v>8959.75</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>117.51</v>
+        <v>116.91</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1309.91</v>
+        <v>1303.18</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>114.57</v>
+        <v>113.99</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>698.53</v>
+        <v>694.9400000000001</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>139.26</v>
+        <v>138.54</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>156.05</v>
+        <v>155.25</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>499.81</v>
+        <v>497.24</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>426.94</v>
+        <v>424.74</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>347.96</v>
+        <v>346.17</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>86.18000000000001</v>
+        <v>85.73</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>97.93000000000001</v>
+        <v>97.42</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>532.7</v>
+        <v>529.96</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1391.83</v>
+        <v>1384.68</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>63.91</v>
+        <v>63.58</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>104.6</v>
+        <v>104.07</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>13489.85</v>
+        <v>13420.54</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>260.97</v>
+        <v>259.63</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>130.48</v>
+        <v>129.81</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>173.98</v>
+        <v>173.09</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>173.98</v>
+        <v>173.09</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>173.98</v>
+        <v>173.09</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2174.74</v>
+        <v>2163.57</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>113.32</v>
+        <v>112.73</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2800.46</v>
+        <v>2786.07</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>391.88</v>
+        <v>389.87</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>284.62</v>
+        <v>283.16</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>221.59</v>
+        <v>220.46</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>193.93</v>
+        <v>192.93</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>156.05</v>
+        <v>155.25</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>494.47</v>
+        <v>491.93</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>86.98999999999999</v>
+        <v>86.54000000000001</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1647.72</v>
+        <v>1639.25</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>920.77</v>
+        <v>916.04</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>6411.99</v>
+        <v>6379.04</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>337.4</v>
+        <v>335.67</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>420.45</v>
+        <v>418.29</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1273.81</v>
+        <v>1267.27</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>716.52</v>
+        <v>712.84</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1023.71</v>
+        <v>1018.45</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2495.74</v>
+        <v>2482.91</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1306.88</v>
+        <v>1300.16</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>586.04</v>
+        <v>583.02</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>3708.06</v>
+        <v>3689.01</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>10072.49</v>
+        <v>10020.73</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>152.23</v>
+        <v>151.45</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>4230.15</v>
+        <v>4208.42</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>174.04</v>
+        <v>173.15</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>3998.47</v>
+        <v>3977.93</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>191.78</v>
+        <v>190.8</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>130.48</v>
+        <v>129.81</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>408.84</v>
+        <v>406.74</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1001.65</v>
+        <v>996.51</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>3605.28</v>
+        <v>3586.75</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>830.98</v>
+        <v>826.71</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1356.43</v>
+        <v>1349.46</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>618.08</v>
+        <v>614.91</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>156.68</v>
+        <v>155.88</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>16189.36</v>
+        <v>16106.18</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>106.83</v>
+        <v>106.28</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2635</v>
+        <v>2621.46</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>455.3</v>
+        <v>452.96</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1043.88</v>
+        <v>1038.51</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>86.98999999999999</v>
+        <v>86.54000000000001</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>241</v>
+        <v>238.6</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>3222.69</v>
+        <v>3190.52</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>17723.48</v>
+        <v>17546.6</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>783.42</v>
+        <v>775.6</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>119.97</v>
+        <v>118.78</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>33953.43</v>
+        <v>33614.58</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>508.53</v>
+        <v>503.45</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>2433.93</v>
+        <v>2409.64</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>169.97</v>
+        <v>168.28</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>2417.4</v>
+        <v>2393.27</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>373.39</v>
+        <v>369.67</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>13749.13</v>
+        <v>13611.92</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2301.92</v>
+        <v>2278.95</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>49980.9</v>
+        <v>49482.08</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>2741.95</v>
+        <v>2714.59</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1759.45</v>
+        <v>1741.89</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>958.92</v>
+        <v>949.35</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>455.3</v>
+        <v>450.75</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>4705.58</v>
+        <v>4658.62</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>376.45</v>
+        <v>372.69</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>195.85</v>
+        <v>193.9</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>16360.16</v>
+        <v>16196.88</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>6506.67</v>
+        <v>6441.74</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>55.4</v>
+        <v>54.85</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>86.98999999999999</v>
+        <v>86.12</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>89.97</v>
+        <v>89.06999999999999</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1432.53</v>
+        <v>1418.23</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>302.17</v>
+        <v>299.16</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>10846.32</v>
+        <v>10738.08</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>2140.78</v>
+        <v>2119.42</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>2140.23</v>
+        <v>2118.87</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>54.09</v>
+        <v>53.55</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1286.77</v>
+        <v>1273.93</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>260.97</v>
+        <v>258.36</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>7930.57</v>
+        <v>7851.43</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>249.9</v>
+        <v>247.41</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>460.38</v>
+        <v>455.79</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>830.98</v>
+        <v>822.6900000000001</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1301.33</v>
+        <v>1288.35</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1917.84</v>
+        <v>1898.7</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>7466.93</v>
+        <v>7392.41</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>170.42</v>
+        <v>168.72</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1472.72</v>
+        <v>1458.02</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>342.62</v>
+        <v>339.2</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>571.11</v>
+        <v>565.41</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>2179.17</v>
+        <v>2157.42</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1230.06</v>
+        <v>1217.79</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>430.73</v>
+        <v>426.43</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>564.67</v>
+        <v>559.03</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>75.54000000000001</v>
+        <v>74.79000000000001</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>276.93</v>
+        <v>274.17</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>235.77</v>
+        <v>233.42</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>577.28</v>
+        <v>571.52</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>1053.27</v>
+        <v>1042.24</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>7911.58</v>
+        <v>7828.73</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>372.75</v>
+        <v>368.84</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>1227.01</v>
+        <v>1214.16</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2499.04</v>
+        <v>2472.87</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>550.55</v>
+        <v>544.79</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>581.23</v>
+        <v>575.14</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>257.24</v>
+        <v>254.55</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>5140.67</v>
+        <v>5086.83</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>2686</v>
+        <v>2657.87</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>1255.25</v>
+        <v>1242.1</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>3349.68</v>
+        <v>3314.6</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>3205.84</v>
+        <v>3172.26</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>107.26</v>
+        <v>106.13</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>281.57</v>
+        <v>278.62</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>128.24</v>
+        <v>126.9</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>460.38</v>
+        <v>455.56</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>2112.83</v>
+        <v>2090.7</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1566.83</v>
+        <v>1550.42</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>4161.26</v>
+        <v>4117.68</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>3329.52</v>
+        <v>3294.65</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>144.6</v>
+        <v>143.09</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>447.67</v>
+        <v>442.98</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>189.5</v>
+        <v>187.51</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>21465.27</v>
+        <v>21240.48</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>283.29</v>
+        <v>280.32</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1212.77</v>
+        <v>1200.07</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>11183.73</v>
+        <v>11066.61</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>2654.17</v>
+        <v>2626.38</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>1838.23</v>
+        <v>1818.98</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>114.31</v>
+        <v>113.11</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>836.83</v>
+        <v>828.0700000000001</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>170.32</v>
+        <v>168.53</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1508.2</v>
+        <v>1492.41</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>732.54</v>
+        <v>724.87</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>134.74</v>
+        <v>133.33</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>248.76</v>
+        <v>246.15</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>196.36</v>
+        <v>194.31</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>108.74</v>
+        <v>107.6</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>4743.73</v>
+        <v>4694.06</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>304.46</v>
+        <v>301.28</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>196.36</v>
+        <v>194.31</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>783.42</v>
+        <v>775.21</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>1656.92</v>
+        <v>1639.57</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>554.7</v>
+        <v>548.89</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>72.84999999999999</v>
+        <v>72.08</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>4246.81</v>
+        <v>4202.34</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>1153.19</v>
+        <v>1141.11</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>884.65</v>
+        <v>875.38</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>347.96</v>
+        <v>344.31</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>6857.35</v>
+        <v>6785.54</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>572.17</v>
+        <v>566.1799999999999</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>1175.89</v>
+        <v>1163.57</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>102.06</v>
+        <v>100.99</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>163.3</v>
+        <v>161.59</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>75.54000000000001</v>
+        <v>74.75</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>869.13</v>
+        <v>860.03</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>216.99</v>
+        <v>214.72</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>343.72</v>
+        <v>340.12</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>690.58</v>
+        <v>683.34</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>143.46</v>
+        <v>141.95</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>134.25</v>
+        <v>132.84</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>122.47</v>
+        <v>121.19</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>1138.5</v>
+        <v>1126.57</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>487.09</v>
+        <v>484.43</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>584.51</v>
+        <v>581.3099999999999</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>5328.46</v>
+        <v>5299.33</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>1045.59</v>
+        <v>1039.87</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>1994.15</v>
+        <v>1983.25</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>487.09</v>
+        <v>484.43</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>472.93</v>
+        <v>470.34</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>280.05</v>
+        <v>278.51</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>16889.22</v>
+        <v>16796.9</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>422.23</v>
+        <v>419.92</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>1163.68</v>
+        <v>1157.32</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>2028.49</v>
+        <v>2017.4</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>690.58</v>
+        <v>686.8</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>521.9400000000001</v>
+        <v>519.09</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>422.23</v>
+        <v>419.92</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>87.23999999999999</v>
+        <v>86.77</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>442.58</v>
+        <v>440.16</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>2301.16</v>
+        <v>2288.58</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>888.66</v>
+        <v>883.8</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>811.8</v>
+        <v>807.36</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>534.15</v>
+        <v>531.23</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>783.42</v>
+        <v>779.13</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>3937.91</v>
+        <v>3916.39</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>21360.19</v>
+        <v>21243.44</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>1854.13</v>
+        <v>1843.99</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>360.96</v>
+        <v>358.98</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>154.01</v>
+        <v>153.17</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>363.7</v>
+        <v>361.72</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>525.24</v>
+        <v>522.37</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>698.21</v>
+        <v>694.39</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>218.11</v>
+        <v>216.92</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>2479.97</v>
+        <v>2466.41</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>1030.9</v>
+        <v>1025.27</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>506.68</v>
+        <v>503.91</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>9402.559999999999</v>
+        <v>9351.16</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>5460.04</v>
+        <v>5430.19</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>3764.15</v>
+        <v>3743.58</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>6927.27</v>
+        <v>6889.41</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>346.24</v>
+        <v>344.35</v>
       </c>
     </row>
     <row r="282">
@@ -17645,7 +17645,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>188.36</v>
+        <v>187.33</v>
       </c>
     </row>
     <row r="283">
@@ -17706,7 +17706,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>2108.83</v>
+        <v>2097.3</v>
       </c>
     </row>
     <row r="284">
@@ -17767,7 +17767,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>602.8200000000001</v>
+        <v>599.53</v>
       </c>
     </row>
     <row r="285">
@@ -17828,7 +17828,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>1958.54</v>
+        <v>1947.83</v>
       </c>
     </row>
     <row r="286">
@@ -17889,7 +17889,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>260.08</v>
+        <v>258.66</v>
       </c>
     </row>
     <row r="287">
@@ -17950,7 +17950,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>4603.84</v>
+        <v>4578.67</v>
       </c>
     </row>
     <row r="288">
@@ -18011,7 +18011,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>527.03</v>
+        <v>524.14</v>
       </c>
     </row>
     <row r="289">
@@ -18072,7 +18072,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>1880.2</v>
+        <v>1869.92</v>
       </c>
     </row>
     <row r="290">
@@ -18133,7 +18133,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>290.61</v>
+        <v>289.03</v>
       </c>
     </row>
     <row r="291">
@@ -18194,7 +18194,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>2174.74</v>
+        <v>2162.85</v>
       </c>
     </row>
     <row r="292">
@@ -18255,7 +18255,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>18637.24</v>
+        <v>18535.38</v>
       </c>
     </row>
     <row r="293">
@@ -18316,7 +18316,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>144.6</v>
+        <v>143.81</v>
       </c>
     </row>
     <row r="294">
@@ -18377,7 +18377,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>241</v>
+        <v>239.68</v>
       </c>
     </row>
     <row r="295">
@@ -18438,7 +18438,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>1872.04</v>
+        <v>1861.81</v>
       </c>
     </row>
     <row r="296">
@@ -18499,7 +18499,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>514.1799999999999</v>
+        <v>511.37</v>
       </c>
     </row>
     <row r="297">
@@ -18560,7 +18560,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>313.37</v>
+        <v>311.65</v>
       </c>
     </row>
     <row r="298">
@@ -18621,7 +18621,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>260.97</v>
+        <v>259.54</v>
       </c>
     </row>
     <row r="299">
@@ -18682,7 +18682,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>107.26</v>
+        <v>106.67</v>
       </c>
     </row>
     <row r="300">
@@ -18743,7 +18743,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>2142.34</v>
+        <v>2130.63</v>
       </c>
     </row>
     <row r="301">
@@ -18804,7 +18804,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>1020.6</v>
+        <v>1015.02</v>
       </c>
     </row>
     <row r="302">
@@ -18865,7 +18865,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>1741.5</v>
+        <v>1731.98</v>
       </c>
     </row>
     <row r="303">
@@ -18926,7 +18926,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>283.29</v>
+        <v>281.74</v>
       </c>
     </row>
     <row r="304">
@@ -18987,7 +18987,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>24182.39</v>
+        <v>24050.21</v>
       </c>
     </row>
     <row r="305">
@@ -19048,7 +19048,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>134.49</v>
+        <v>133.76</v>
       </c>
     </row>
     <row r="306">
@@ -19109,7 +19109,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>168.43</v>
+        <v>167.51</v>
       </c>
     </row>
     <row r="307">
@@ -19170,7 +19170,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>1999.13</v>
+        <v>1976.86</v>
       </c>
     </row>
     <row r="308">
@@ -19231,7 +19231,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>1266.69</v>
+        <v>1252.58</v>
       </c>
     </row>
     <row r="309">
@@ -19292,7 +19292,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>4486.83</v>
+        <v>4436.84</v>
       </c>
     </row>
     <row r="310">
@@ -19353,7 +19353,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>304.46</v>
+        <v>301.07</v>
       </c>
     </row>
     <row r="311">
@@ -19414,7 +19414,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>250.14</v>
+        <v>247.35</v>
       </c>
     </row>
     <row r="312">
@@ -19475,7 +19475,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>466.74</v>
+        <v>461.54</v>
       </c>
     </row>
     <row r="313">
@@ -19536,7 +19536,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>24500.67</v>
+        <v>24227.69</v>
       </c>
     </row>
     <row r="314">
@@ -19597,7 +19597,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>124.33</v>
+        <v>122.94</v>
       </c>
     </row>
     <row r="315">
@@ -19658,7 +19658,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>9073.08</v>
+        <v>8972</v>
       </c>
     </row>
     <row r="316">
@@ -19719,7 +19719,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>876.76</v>
+        <v>867</v>
       </c>
     </row>
     <row r="317">
@@ -19780,7 +19780,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>176.01</v>
+        <v>174.05</v>
       </c>
     </row>
     <row r="318">
@@ -19841,7 +19841,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>1377.34</v>
+        <v>1361.99</v>
       </c>
     </row>
     <row r="319">
@@ -19902,7 +19902,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>558.1799999999999</v>
+        <v>551.96</v>
       </c>
     </row>
     <row r="320">
@@ -19963,7 +19963,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>1688.92</v>
+        <v>1670.1</v>
       </c>
     </row>
     <row r="321">
@@ -20024,7 +20024,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>1006.43</v>
+        <v>995.22</v>
       </c>
     </row>
     <row r="322">
@@ -20085,7 +20085,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>923.3099999999999</v>
+        <v>913.02</v>
       </c>
     </row>
     <row r="323">
@@ -20146,7 +20146,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>221.8</v>
+        <v>219.33</v>
       </c>
     </row>
     <row r="324">
@@ -20207,7 +20207,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>162.28</v>
+        <v>160.47</v>
       </c>
     </row>
     <row r="325">
@@ -20268,7 +20268,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>5259.06</v>
+        <v>5200.46</v>
       </c>
     </row>
     <row r="326">
@@ -20329,7 +20329,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>698.33</v>
+        <v>690.55</v>
       </c>
     </row>
     <row r="327">
@@ -20390,7 +20390,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>3150.19</v>
+        <v>3115.09</v>
       </c>
     </row>
     <row r="328">
@@ -20451,7 +20451,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>165.33</v>
+        <v>163.49</v>
       </c>
     </row>
     <row r="329">
@@ -20512,7 +20512,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>4222.3</v>
+        <v>4175.26</v>
       </c>
     </row>
     <row r="330">
@@ -20573,7 +20573,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>277.74</v>
+        <v>274.64</v>
       </c>
     </row>
     <row r="331">
@@ -20634,7 +20634,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>67.23999999999999</v>
+        <v>66.48999999999999</v>
       </c>
     </row>
     <row r="332">
@@ -20695,7 +20695,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>227.39</v>
+        <v>224.86</v>
       </c>
     </row>
     <row r="333">
@@ -20756,7 +20756,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>1688.92</v>
+        <v>1670.1</v>
       </c>
     </row>
     <row r="334">
@@ -20817,7 +20817,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>236.36</v>
+        <v>233.73</v>
       </c>
     </row>
     <row r="335">
@@ -20878,7 +20878,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>608.55</v>
+        <v>601.77</v>
       </c>
     </row>
     <row r="336">
@@ -20939,7 +20939,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>358.13</v>
+        <v>354.14</v>
       </c>
     </row>
     <row r="337">
@@ -21000,7 +21000,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>355.21</v>
+        <v>351.25</v>
       </c>
     </row>
     <row r="338">
@@ -21061,7 +21061,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>191.28</v>
+        <v>189.14</v>
       </c>
     </row>
     <row r="339">
@@ -21122,7 +21122,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>73.91</v>
+        <v>73.09</v>
       </c>
     </row>
     <row r="340">
@@ -21183,7 +21183,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>389.78</v>
+        <v>385.44</v>
       </c>
     </row>
     <row r="341">
@@ -21244,7 +21244,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>3106.95</v>
+        <v>3072.34</v>
       </c>
     </row>
     <row r="342">
@@ -21305,7 +21305,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>1266.67</v>
+        <v>1252.55</v>
       </c>
     </row>
     <row r="343">
@@ -21366,7 +21366,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>860.74</v>
+        <v>851.15</v>
       </c>
     </row>
     <row r="344">
@@ -21427,7 +21427,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>80.69</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="345">
@@ -21488,7 +21488,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>134.49</v>
+        <v>132.99</v>
       </c>
     </row>
     <row r="346">
@@ -21549,7 +21549,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>251.05</v>
+        <v>248.25</v>
       </c>
     </row>
     <row r="347">
@@ -21610,7 +21610,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>134.49</v>
+        <v>132.99</v>
       </c>
     </row>
     <row r="348">
@@ -21671,7 +21671,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>161.39</v>
+        <v>159.59</v>
       </c>
     </row>
     <row r="349">
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>134.49</v>
+        <v>132.99</v>
       </c>
     </row>
     <row r="350">
@@ -21793,7 +21793,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>662.86</v>
+        <v>655.48</v>
       </c>
     </row>
     <row r="351">
@@ -21854,7 +21854,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>761.16</v>
+        <v>752.6799999999999</v>
       </c>
     </row>
     <row r="352">
@@ -21915,7 +21915,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>585.46</v>
+        <v>578.9400000000001</v>
       </c>
     </row>
     <row r="353">
@@ -21976,7 +21976,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>418.42</v>
+        <v>413.75</v>
       </c>
     </row>
     <row r="354">
@@ -22037,7 +22037,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>1515.96</v>
+        <v>1499.07</v>
       </c>
     </row>
     <row r="355">
@@ -22098,7 +22098,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>1093.73</v>
+        <v>1081.54</v>
       </c>
     </row>
     <row r="356">
@@ -22159,7 +22159,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>118.66</v>
+        <v>117.33</v>
       </c>
     </row>
     <row r="357">
@@ -22220,7 +22220,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>482</v>
+        <v>476.63</v>
       </c>
     </row>
     <row r="358">
@@ -22281,7 +22281,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>584.51</v>
+        <v>578</v>
       </c>
     </row>
     <row r="359">
@@ -22342,7 +22342,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>5064.22</v>
+        <v>5007.8</v>
       </c>
     </row>
     <row r="360">
@@ -22403,7 +22403,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>487.09</v>
+        <v>481.66</v>
       </c>
     </row>
     <row r="361">
@@ -22464,7 +22464,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>578.5700000000001</v>
+        <v>572.12</v>
       </c>
     </row>
     <row r="362">
@@ -22525,7 +22525,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>608.55</v>
+        <v>601.77</v>
       </c>
     </row>
     <row r="363">
@@ -22586,7 +22586,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>407.91</v>
+        <v>403.36</v>
       </c>
     </row>
     <row r="364">
@@ -22647,7 +22647,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>354.06</v>
+        <v>350.12</v>
       </c>
     </row>
     <row r="365">
@@ -22708,7 +22708,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>1613.89</v>
+        <v>1595.91</v>
       </c>
     </row>
     <row r="366">
@@ -22769,7 +22769,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>167.11</v>
+        <v>165.25</v>
       </c>
     </row>
     <row r="367">
@@ -22830,7 +22830,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>4161.26</v>
+        <v>4114.9</v>
       </c>
     </row>
     <row r="368">
@@ -22891,7 +22891,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>652.41</v>
+        <v>645.14</v>
       </c>
     </row>
     <row r="369">
@@ -22952,7 +22952,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>290.72</v>
+        <v>289.13</v>
       </c>
     </row>
     <row r="370">
@@ -23013,7 +23013,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>239.09</v>
+        <v>237.78</v>
       </c>
     </row>
     <row r="371">
@@ -23074,7 +23074,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>764.8</v>
+        <v>760.61</v>
       </c>
     </row>
     <row r="372">
@@ -23135,7 +23135,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>161.16</v>
+        <v>160.28</v>
       </c>
     </row>
     <row r="373">
@@ -23196,7 +23196,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>454.98</v>
+        <v>452.49</v>
       </c>
     </row>
     <row r="374">
@@ -23257,7 +23257,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>4164.49</v>
+        <v>4141.68</v>
       </c>
     </row>
     <row r="375">
@@ -23318,7 +23318,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>827.27</v>
+        <v>822.74</v>
       </c>
     </row>
     <row r="376">
@@ -23379,7 +23379,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>466.74</v>
+        <v>464.19</v>
       </c>
     </row>
     <row r="377">
@@ -23440,7 +23440,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>442.58</v>
+        <v>440.16</v>
       </c>
     </row>
     <row r="378">
@@ -23501,7 +23501,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>147.78</v>
+        <v>146.97</v>
       </c>
     </row>
     <row r="379">
@@ -23562,7 +23562,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>205.39</v>
+        <v>204.27</v>
       </c>
     </row>
     <row r="380">
@@ -23623,7 +23623,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>363.76</v>
+        <v>361.76</v>
       </c>
     </row>
     <row r="381">
@@ -23684,7 +23684,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>138.12</v>
+        <v>137.36</v>
       </c>
     </row>
     <row r="382">
@@ -23745,7 +23745,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>1420.83</v>
+        <v>1413.05</v>
       </c>
     </row>
     <row r="383">
@@ -23806,7 +23806,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>42.22</v>
+        <v>41.99</v>
       </c>
     </row>
     <row r="384">
@@ -23867,7 +23867,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>328.63</v>
+        <v>326.83</v>
       </c>
     </row>
     <row r="385">
@@ -23928,7 +23928,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>280.05</v>
+        <v>278.51</v>
       </c>
     </row>
     <row r="386">
@@ -23989,7 +23989,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>38.06</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="387">
@@ -24050,7 +24050,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>211.12</v>
+        <v>209.96</v>
       </c>
     </row>
     <row r="388">
@@ -24111,7 +24111,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>118.66</v>
+        <v>118.01</v>
       </c>
     </row>
     <row r="389">
@@ -24172,7 +24172,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>2333.71</v>
+        <v>2320.93</v>
       </c>
     </row>
     <row r="390">
@@ -24233,7 +24233,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>121.93</v>
+        <v>121.26</v>
       </c>
     </row>
     <row r="391">
@@ -24294,7 +24294,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>287.55</v>
+        <v>285.97</v>
       </c>
     </row>
     <row r="392">
@@ -24355,7 +24355,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>256.01</v>
+        <v>254.61</v>
       </c>
     </row>
     <row r="393">
@@ -24416,7 +24416,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>2271.91</v>
+        <v>2259.46</v>
       </c>
     </row>
     <row r="394">
@@ -24477,7 +24477,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>5183.15</v>
+        <v>5154.76</v>
       </c>
     </row>
     <row r="395">
@@ -24538,7 +24538,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>696.11</v>
+        <v>692.3</v>
       </c>
     </row>
     <row r="396">
@@ -24599,7 +24599,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>6298.52</v>
+        <v>6264.03</v>
       </c>
     </row>
     <row r="397">
@@ -24660,7 +24660,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>447.67</v>
+        <v>445.21</v>
       </c>
     </row>
     <row r="398">
@@ -24721,7 +24721,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>126.67</v>
+        <v>125.98</v>
       </c>
     </row>
     <row r="399">
@@ -24782,7 +24782,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>1831.4</v>
+        <v>1821.37</v>
       </c>
     </row>
     <row r="400">
@@ -24843,7 +24843,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>1161.13</v>
+        <v>1154.77</v>
       </c>
     </row>
     <row r="401">
@@ -24904,7 +24904,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>36563.63</v>
+        <v>36363.39</v>
       </c>
     </row>
     <row r="402">
@@ -24965,7 +24965,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>974.1799999999999</v>
+        <v>968.85</v>
       </c>
     </row>
     <row r="403">
@@ -25026,7 +25026,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>572.3</v>
+        <v>569.17</v>
       </c>
     </row>
     <row r="404">
@@ -25087,7 +25087,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>174.17</v>
+        <v>173.22</v>
       </c>
     </row>
     <row r="405">
@@ -25148,7 +25148,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>110.64</v>
+        <v>110.04</v>
       </c>
     </row>
     <row r="406">
@@ -25209,7 +25209,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>469.29</v>
+        <v>466.72</v>
       </c>
     </row>
     <row r="407">
@@ -25270,7 +25270,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="408">
@@ -25331,7 +25331,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>902.96</v>
+        <v>898.02</v>
       </c>
     </row>
     <row r="409">
@@ -25392,7 +25392,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>1292.64</v>
+        <v>1285.56</v>
       </c>
     </row>
     <row r="410">
@@ -25453,7 +25453,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>1622.79</v>
+        <v>1613.9</v>
       </c>
     </row>
     <row r="411">
@@ -25514,7 +25514,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>164.31</v>
+        <v>163.41</v>
       </c>
     </row>
     <row r="412">
@@ -25575,7 +25575,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>1687.68</v>
+        <v>1678.43</v>
       </c>
     </row>
     <row r="413">
@@ -25636,7 +25636,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>717.28</v>
+        <v>713.35</v>
       </c>
     </row>
     <row r="414">
@@ -25697,7 +25697,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>164.25</v>
+        <v>163.35</v>
       </c>
     </row>
     <row r="415">
@@ -25758,7 +25758,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>151.6</v>
+        <v>150.77</v>
       </c>
     </row>
     <row r="416">
@@ -25819,7 +25819,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>37726.04</v>
+        <v>37519.43</v>
       </c>
     </row>
     <row r="417">
@@ -25880,7 +25880,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>17876.12</v>
+        <v>17778.22</v>
       </c>
     </row>
     <row r="418">
@@ -25941,7 +25941,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>7039.87</v>
+        <v>7001.32</v>
       </c>
     </row>
     <row r="419">
@@ -26002,7 +26002,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>153.14</v>
+        <v>152.3</v>
       </c>
     </row>
     <row r="420">
@@ -26063,7 +26063,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>118.66</v>
+        <v>118.01</v>
       </c>
     </row>
     <row r="421">
@@ -26124,7 +26124,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>766.88</v>
+        <v>762.6799999999999</v>
       </c>
     </row>
     <row r="422">
@@ -26185,7 +26185,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>169.97</v>
+        <v>169.04</v>
       </c>
     </row>
     <row r="423">
@@ -26246,7 +26246,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>7880.73</v>
+        <v>7837.57</v>
       </c>
     </row>
     <row r="424">
@@ -26307,7 +26307,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>328.63</v>
+        <v>326.83</v>
       </c>
     </row>
     <row r="425">
@@ -26368,7 +26368,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>466.74</v>
+        <v>464.19</v>
       </c>
     </row>
     <row r="426">
@@ -26429,7 +26429,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>2273.94</v>
+        <v>2261.49</v>
       </c>
     </row>
     <row r="427">
@@ -26490,7 +26490,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>164.31</v>
+        <v>163.41</v>
       </c>
     </row>
     <row r="428">
@@ -26551,7 +26551,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>487.09</v>
+        <v>484.42</v>
       </c>
     </row>
     <row r="429">
@@ -26612,7 +26612,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>923.3099999999999</v>
+        <v>918.25</v>
       </c>
     </row>
     <row r="430">
@@ -26673,7 +26673,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>575.1</v>
+        <v>571.95</v>
       </c>
     </row>
     <row r="431">
@@ -26734,7 +26734,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>730.64</v>
+        <v>726.64</v>
       </c>
     </row>
     <row r="432">
@@ -26795,7 +26795,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>730.64</v>
+        <v>726.64</v>
       </c>
     </row>
     <row r="433">
@@ -26856,7 +26856,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>1107.97</v>
+        <v>1101.91</v>
       </c>
     </row>
     <row r="434">
@@ -26917,7 +26917,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>533.85</v>
+        <v>530.9299999999999</v>
       </c>
     </row>
     <row r="435">
@@ -26978,7 +26978,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>461.66</v>
+        <v>459.13</v>
       </c>
     </row>
     <row r="436">
@@ -27039,7 +27039,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>480.73</v>
+        <v>478.1</v>
       </c>
     </row>
     <row r="437">
@@ -27100,7 +27100,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>722.17</v>
+        <v>718.21</v>
       </c>
     </row>
     <row r="438">
@@ -27161,7 +27161,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>1320.11</v>
+        <v>1312.88</v>
       </c>
     </row>
     <row r="439">
@@ -27222,7 +27222,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>1495.61</v>
+        <v>1487.42</v>
       </c>
     </row>
     <row r="440">
@@ -27283,7 +27283,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>286.91</v>
+        <v>285.34</v>
       </c>
     </row>
     <row r="441">
@@ -27344,7 +27344,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>1688.92</v>
+        <v>1679.67</v>
       </c>
     </row>
     <row r="442">
@@ -27405,7 +27405,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>534.15</v>
+        <v>531.22</v>
       </c>
     </row>
     <row r="443">
@@ -27466,7 +27466,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>889.65</v>
+        <v>884.78</v>
       </c>
     </row>
     <row r="444">
@@ -27527,7 +27527,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>150.02</v>
+        <v>149.83</v>
       </c>
     </row>
     <row r="445">
@@ -27588,7 +27588,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>640.8099999999999</v>
+        <v>639.99</v>
       </c>
     </row>
     <row r="446">
@@ -27649,7 +27649,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>30230.3</v>
+        <v>30191.83</v>
       </c>
     </row>
     <row r="447">
@@ -27710,7 +27710,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>4309.9</v>
+        <v>4304.41</v>
       </c>
     </row>
     <row r="448">
@@ -27771,7 +27771,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>6085.46</v>
+        <v>6077.71</v>
       </c>
     </row>
     <row r="449">
@@ -27832,7 +27832,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>81.72</v>
+        <v>81.62</v>
       </c>
     </row>
     <row r="450">
@@ -27893,7 +27893,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>909.58</v>
+        <v>908.42</v>
       </c>
     </row>
     <row r="451">
@@ -27954,7 +27954,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>558.3099999999999</v>
+        <v>557.6</v>
       </c>
     </row>
     <row r="452">
@@ -28015,7 +28015,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>303.55</v>
+        <v>303.17</v>
       </c>
     </row>
     <row r="453">
@@ -28076,7 +28076,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>2024.8</v>
+        <v>2022.22</v>
       </c>
     </row>
     <row r="454">
@@ -28137,7 +28137,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>1561.38</v>
+        <v>1559.4</v>
       </c>
     </row>
     <row r="455">
@@ -28198,7 +28198,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>1013.35</v>
+        <v>1012.06</v>
       </c>
     </row>
     <row r="456">
@@ -28259,7 +28259,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>552.46</v>
+        <v>551.76</v>
       </c>
     </row>
     <row r="457">
@@ -28320,7 +28320,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>1497.01</v>
+        <v>1495.11</v>
       </c>
     </row>
     <row r="458">
@@ -28381,7 +28381,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>167.49</v>
+        <v>167.28</v>
       </c>
     </row>
     <row r="459">
@@ -28442,7 +28442,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>534.3099999999999</v>
+        <v>533.63</v>
       </c>
     </row>
     <row r="460">
@@ -28503,7 +28503,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>126.57</v>
+        <v>126.41</v>
       </c>
     </row>
     <row r="461">
@@ -28564,7 +28564,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>1893.5</v>
+        <v>1891.09</v>
       </c>
     </row>
     <row r="462">
@@ -28625,7 +28625,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>1096.78</v>
+        <v>1095.39</v>
       </c>
     </row>
     <row r="463">
@@ -28686,7 +28686,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>1196.49</v>
+        <v>1194.97</v>
       </c>
     </row>
     <row r="464">
@@ -28747,7 +28747,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>365.32</v>
+        <v>364.85</v>
       </c>
     </row>
     <row r="465">
@@ -28808,7 +28808,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>633.35</v>
+        <v>632.54</v>
       </c>
     </row>
     <row r="466">
@@ -28869,7 +28869,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>667.52</v>
+        <v>666.67</v>
       </c>
     </row>
     <row r="467">
@@ -28930,7 +28930,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>337.78</v>
+        <v>337.35</v>
       </c>
     </row>
     <row r="468">
@@ -28991,7 +28991,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>97.42</v>
+        <v>97.29000000000001</v>
       </c>
     </row>
     <row r="469">
@@ -29052,7 +29052,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>221.29</v>
+        <v>221.01</v>
       </c>
     </row>
     <row r="470">
@@ -29113,7 +29113,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>1163.64</v>
+        <v>1162.16</v>
       </c>
     </row>
     <row r="471">
@@ -29174,7 +29174,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>1046.46</v>
+        <v>1045.12</v>
       </c>
     </row>
     <row r="472">
@@ -29235,7 +29235,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>1826.78</v>
+        <v>1824.46</v>
       </c>
     </row>
     <row r="473">
@@ -29296,7 +29296,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>619.61</v>
+        <v>618.8200000000001</v>
       </c>
     </row>
     <row r="474">
@@ -29357,7 +29357,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>111.92</v>
+        <v>111.77</v>
       </c>
     </row>
     <row r="475">
@@ -29418,7 +29418,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>1777.37</v>
+        <v>1775.11</v>
       </c>
     </row>
     <row r="476">
@@ -29479,7 +29479,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>2315.54</v>
+        <v>2312.6</v>
       </c>
     </row>
     <row r="477">
@@ -29540,7 +29540,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>1227.01</v>
+        <v>1225.45</v>
       </c>
     </row>
     <row r="478">
@@ -29601,7 +29601,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>627.62</v>
+        <v>626.8200000000001</v>
       </c>
     </row>
     <row r="479">
@@ -29662,7 +29662,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>1419.3</v>
+        <v>1417.5</v>
       </c>
     </row>
     <row r="480">
@@ -29723,7 +29723,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>487.09</v>
+        <v>486.47</v>
       </c>
     </row>
     <row r="481">
@@ -29784,7 +29784,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>186.7</v>
+        <v>186.46</v>
       </c>
     </row>
     <row r="482">
@@ -29845,7 +29845,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>165.33</v>
+        <v>165.12</v>
       </c>
     </row>
     <row r="483">
@@ -29906,7 +29906,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>378.99</v>
+        <v>378.51</v>
       </c>
     </row>
     <row r="484">
@@ -29967,7 +29967,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>177.03</v>
+        <v>176.81</v>
       </c>
     </row>
     <row r="485">
@@ -30028,7 +30028,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>292.25</v>
+        <v>291.88</v>
       </c>
     </row>
     <row r="486">
@@ -30089,7 +30089,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>1232.1</v>
+        <v>1230.53</v>
       </c>
     </row>
     <row r="487">
@@ -30150,7 +30150,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>166.88</v>
+        <v>166.67</v>
       </c>
     </row>
     <row r="488">
@@ -30211,7 +30211,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>309.81</v>
+        <v>309.41</v>
       </c>
     </row>
     <row r="489">
@@ -30272,7 +30272,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>5344.03</v>
+        <v>5337.22</v>
       </c>
     </row>
     <row r="490">
@@ -30333,7 +30333,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>54.86</v>
+        <v>54.79</v>
       </c>
     </row>
     <row r="491">
@@ -30394,7 +30394,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>633.35</v>
+        <v>632.54</v>
       </c>
     </row>
     <row r="492">
@@ -30455,7 +30455,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>977.04</v>
+        <v>975.8</v>
       </c>
     </row>
     <row r="493">
@@ -30516,7 +30516,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>1522.32</v>
+        <v>1520.38</v>
       </c>
     </row>
     <row r="494">
@@ -30577,7 +30577,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>223.83</v>
+        <v>223.55</v>
       </c>
     </row>
     <row r="495">
@@ -30638,7 +30638,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>152.23</v>
+        <v>152.04</v>
       </c>
     </row>
     <row r="496">
@@ -30699,7 +30699,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>492.43</v>
+        <v>491.81</v>
       </c>
     </row>
     <row r="497">
@@ -30760,7 +30760,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>147.78</v>
+        <v>147.59</v>
       </c>
     </row>
     <row r="498">
@@ -30821,7 +30821,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>253.34</v>
+        <v>253.02</v>
       </c>
     </row>
     <row r="499">
@@ -30882,7 +30882,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>2021.95</v>
+        <v>2019.38</v>
       </c>
     </row>
     <row r="500">
@@ -30943,7 +30943,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>3506.29</v>
+        <v>3501.83</v>
       </c>
     </row>
     <row r="501">
@@ -31004,7 +31004,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>246.47</v>
+        <v>246.16</v>
       </c>
     </row>
     <row r="502">
@@ -31065,7 +31065,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>1405.32</v>
+        <v>1403.53</v>
       </c>
     </row>
     <row r="503">
@@ -31126,7 +31126,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>1396.41</v>
+        <v>1394.64</v>
       </c>
     </row>
     <row r="504">
@@ -31187,7 +31187,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>147.78</v>
+        <v>147.59</v>
       </c>
     </row>
     <row r="505">
@@ -31248,7 +31248,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>956.38</v>
+        <v>959.79</v>
       </c>
     </row>
     <row r="506">
@@ -31309,7 +31309,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>121.71</v>
+        <v>122.14</v>
       </c>
     </row>
     <row r="507">
@@ -31370,7 +31370,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>101.42</v>
+        <v>101.79</v>
       </c>
     </row>
     <row r="508">
@@ -31431,7 +31431,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>1595.32</v>
+        <v>1601.01</v>
       </c>
     </row>
     <row r="509">
@@ -31492,7 +31492,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>199.41</v>
+        <v>200.13</v>
       </c>
     </row>
     <row r="510">
@@ -31553,7 +31553,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>24555.12</v>
+        <v>24642.76</v>
       </c>
     </row>
     <row r="511">
@@ -31614,7 +31614,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>1068.29</v>
+        <v>1072.11</v>
       </c>
     </row>
     <row r="512">
@@ -31675,7 +31675,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>161.58</v>
+        <v>162.16</v>
       </c>
     </row>
     <row r="513">
@@ -31736,7 +31736,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>115.23</v>
+        <v>115.64</v>
       </c>
     </row>
     <row r="514">
@@ -31797,7 +31797,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>7191.34</v>
+        <v>7217</v>
       </c>
     </row>
     <row r="515">
@@ -31858,7 +31858,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>179.07</v>
+        <v>179.71</v>
       </c>
     </row>
     <row r="516">
@@ -31919,7 +31919,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>331.93</v>
+        <v>333.12</v>
       </c>
     </row>
     <row r="517">
@@ -31980,7 +31980,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>454.79</v>
+        <v>456.41</v>
       </c>
     </row>
     <row r="518">
@@ -32041,7 +32041,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>68.68000000000001</v>
+        <v>68.92</v>
       </c>
     </row>
     <row r="519">
@@ -32102,7 +32102,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>553.99</v>
+        <v>555.96</v>
       </c>
     </row>
     <row r="520">
@@ -32163,7 +32163,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>1984.69</v>
+        <v>1991.77</v>
       </c>
     </row>
     <row r="521">
@@ -32224,7 +32224,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>2705.65</v>
+        <v>2715.3</v>
       </c>
     </row>
     <row r="522">
@@ -32285,7 +32285,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>152.23</v>
+        <v>152.78</v>
       </c>
     </row>
     <row r="523">
@@ -32346,7 +32346,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>378.99</v>
+        <v>380.34</v>
       </c>
     </row>
     <row r="524">
@@ -32407,7 +32407,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>205.67</v>
+        <v>206.41</v>
       </c>
     </row>
     <row r="525">
@@ -32468,7 +32468,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>3886.02</v>
+        <v>3899.89</v>
       </c>
     </row>
     <row r="526">
@@ -32529,7 +32529,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>331.09</v>
+        <v>332.28</v>
       </c>
     </row>
     <row r="527">
@@ -32590,7 +32590,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>14182</v>
+        <v>14232.61</v>
       </c>
     </row>
     <row r="528">
@@ -32651,7 +32651,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>369.32</v>
+        <v>370.64</v>
       </c>
     </row>
     <row r="529">
@@ -32712,7 +32712,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>19912.46</v>
+        <v>19983.52</v>
       </c>
     </row>
     <row r="530">
@@ -32773,7 +32773,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>141.99</v>
+        <v>142.5</v>
       </c>
     </row>
     <row r="531">
@@ -32834,7 +32834,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>929.99</v>
+        <v>933.3099999999999</v>
       </c>
     </row>
     <row r="532">
@@ -32895,7 +32895,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>2520.72</v>
+        <v>2529.71</v>
       </c>
     </row>
     <row r="533">
@@ -32956,7 +32956,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>3806.43</v>
+        <v>3820.02</v>
       </c>
     </row>
     <row r="534">
@@ -33017,7 +33017,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>2351.23</v>
+        <v>2359.62</v>
       </c>
     </row>
     <row r="535">
@@ -33078,7 +33078,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>885.16</v>
+        <v>888.3200000000001</v>
       </c>
     </row>
     <row r="536">
@@ -33139,7 +33139,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>137.73</v>
+        <v>138.23</v>
       </c>
     </row>
     <row r="537">
@@ -33200,7 +33200,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>3994.15</v>
+        <v>4008.4</v>
       </c>
     </row>
     <row r="538">
@@ -33261,7 +33261,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>4249.25</v>
+        <v>4264.42</v>
       </c>
     </row>
     <row r="539">
@@ -33322,7 +33322,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>55555.1</v>
+        <v>55753.37</v>
       </c>
     </row>
     <row r="540">
@@ -33383,7 +33383,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>1180.46</v>
+        <v>1184.68</v>
       </c>
     </row>
     <row r="541">
@@ -33444,7 +33444,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>988.8099999999999</v>
+        <v>992.34</v>
       </c>
     </row>
     <row r="542">
@@ -33505,7 +33505,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>2273.94</v>
+        <v>2282.06</v>
       </c>
     </row>
     <row r="543">
@@ -33566,7 +33566,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>422.23</v>
+        <v>423.74</v>
       </c>
     </row>
     <row r="544">
@@ -33627,7 +33627,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>817.24</v>
+        <v>820.16</v>
       </c>
     </row>
     <row r="545">
@@ -33688,7 +33688,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>336.19</v>
+        <v>337.39</v>
       </c>
     </row>
     <row r="546">
@@ -33749,7 +33749,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>761.16</v>
+        <v>763.88</v>
       </c>
     </row>
     <row r="547">
@@ -33810,7 +33810,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>316.42</v>
+        <v>317.55</v>
       </c>
     </row>
     <row r="548">
@@ -33871,7 +33871,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>105.56</v>
+        <v>105.93</v>
       </c>
     </row>
     <row r="549">
@@ -33932,7 +33932,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>799.6900000000001</v>
+        <v>802.55</v>
       </c>
     </row>
     <row r="550">
@@ -33993,7 +33993,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>83.77</v>
+        <v>84.06999999999999</v>
       </c>
     </row>
     <row r="551">
@@ -34054,7 +34054,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>734.72</v>
+        <v>737.34</v>
       </c>
     </row>
     <row r="552">
@@ -34115,7 +34115,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>1324.68</v>
+        <v>1329.41</v>
       </c>
     </row>
     <row r="553">
@@ -34176,7 +34176,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>17267.4</v>
+        <v>17329.02</v>
       </c>
     </row>
     <row r="554">
@@ -34237,7 +34237,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>105.56</v>
+        <v>105.93</v>
       </c>
     </row>
     <row r="555">
@@ -34298,7 +34298,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>13320.74</v>
+        <v>13368.28</v>
       </c>
     </row>
     <row r="556">
@@ -34359,7 +34359,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>126.67</v>
+        <v>127.12</v>
       </c>
     </row>
     <row r="557">
@@ -34420,7 +34420,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>1173.72</v>
+        <v>1177.91</v>
       </c>
     </row>
     <row r="558">
@@ -34481,7 +34481,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>671.5</v>
+        <v>673.9</v>
       </c>
     </row>
     <row r="559">
@@ -34542,7 +34542,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>1894.95</v>
+        <v>1901.71</v>
       </c>
     </row>
     <row r="560">
@@ -34603,7 +34603,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>4545.21</v>
+        <v>4561.43</v>
       </c>
     </row>
     <row r="561">
@@ -34664,7 +34664,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>365.74</v>
+        <v>367.04</v>
       </c>
     </row>
     <row r="562">
@@ -34725,7 +34725,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>108.66</v>
+        <v>109.05</v>
       </c>
     </row>
     <row r="563">
@@ -34786,7 +34786,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>679.13</v>
+        <v>681.55</v>
       </c>
     </row>
     <row r="564">
@@ -34847,7 +34847,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>442.58</v>
+        <v>444.16</v>
       </c>
     </row>
     <row r="565">
@@ -34908,7 +34908,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>422.23</v>
+        <v>423.74</v>
       </c>
     </row>
     <row r="566">
@@ -34969,7 +34969,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>253.13</v>
+        <v>254.04</v>
       </c>
     </row>
     <row r="567">
@@ -35030,7 +35030,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>918.22</v>
+        <v>921.5</v>
       </c>
     </row>
     <row r="568">
@@ -35091,7 +35091,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>492.43</v>
+        <v>494.19</v>
       </c>
     </row>
     <row r="569">
@@ -35152,7 +35152,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>199.67</v>
+        <v>200.38</v>
       </c>
     </row>
     <row r="570">
@@ -35213,7 +35213,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>1381.79</v>
+        <v>1386.72</v>
       </c>
     </row>
     <row r="571">
@@ -35274,7 +35274,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>151.6</v>
+        <v>152.14</v>
       </c>
     </row>
     <row r="572">
@@ -35335,7 +35335,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>2791.55</v>
+        <v>2801.52</v>
       </c>
     </row>
     <row r="573">
@@ -35396,7 +35396,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>59.88</v>
+        <v>60.53</v>
       </c>
     </row>
     <row r="574">
@@ -35457,7 +35457,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>204.31</v>
+        <v>206.53</v>
       </c>
     </row>
     <row r="575">
@@ -35518,7 +35518,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>287.55</v>
+        <v>290.68</v>
       </c>
     </row>
     <row r="576">
@@ -35579,7 +35579,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>5714.57</v>
+        <v>5776.72</v>
       </c>
     </row>
     <row r="577">
@@ -35640,7 +35640,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>102.68</v>
+        <v>103.8</v>
       </c>
     </row>
     <row r="578">
@@ -35701,7 +35701,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>495.99</v>
+        <v>501.39</v>
       </c>
     </row>
     <row r="579">
@@ -35762,7 +35762,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>221.76</v>
+        <v>224.17</v>
       </c>
     </row>
     <row r="580">
@@ -35823,7 +35823,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>136.44</v>
+        <v>137.92</v>
       </c>
     </row>
     <row r="581">
@@ -35884,7 +35884,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>1014.88</v>
+        <v>1025.92</v>
       </c>
     </row>
     <row r="582">
@@ -35945,7 +35945,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>1327.74</v>
+        <v>1342.18</v>
       </c>
     </row>
     <row r="583">
@@ -36006,7 +36006,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>3789.9</v>
+        <v>3831.12</v>
       </c>
     </row>
     <row r="584">
@@ -36067,7 +36067,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>64.47</v>
+        <v>65.17</v>
       </c>
     </row>
     <row r="585">
@@ -36128,7 +36128,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>13894.88</v>
+        <v>14046</v>
       </c>
     </row>
     <row r="586">
@@ -36189,7 +36189,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>280.05</v>
+        <v>283.09</v>
       </c>
     </row>
     <row r="587">
@@ -36250,7 +36250,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>284.61</v>
+        <v>287.71</v>
       </c>
     </row>
     <row r="588">
@@ -36311,7 +36311,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>2028.49</v>
+        <v>2050.55</v>
       </c>
     </row>
     <row r="589">
@@ -36372,7 +36372,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>1786.59</v>
+        <v>1806.03</v>
       </c>
     </row>
     <row r="590">
@@ -36433,7 +36433,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>126.67</v>
+        <v>128.05</v>
       </c>
     </row>
     <row r="591">
@@ -36494,7 +36494,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>6333.46</v>
+        <v>6402.34</v>
       </c>
     </row>
     <row r="592">
@@ -36555,7 +36555,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>619.99</v>
+        <v>626.74</v>
       </c>
     </row>
     <row r="593">
@@ -36616,7 +36616,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>671.5</v>
+        <v>678.8</v>
       </c>
     </row>
     <row r="594">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>2492.69</v>
+        <v>2519.8</v>
       </c>
     </row>
     <row r="595">
@@ -36738,7 +36738,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>112.03</v>
+        <v>113.25</v>
       </c>
     </row>
     <row r="596">
@@ -36799,7 +36799,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>113.7</v>
+        <v>114.93</v>
       </c>
     </row>
     <row r="597">
@@ -36860,7 +36860,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>1231.08</v>
+        <v>1244.47</v>
       </c>
     </row>
     <row r="598">
@@ -36921,7 +36921,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>682.1799999999999</v>
+        <v>689.6</v>
       </c>
     </row>
     <row r="599">
@@ -36982,7 +36982,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>284.3</v>
+        <v>287.39</v>
       </c>
     </row>
     <row r="600">
@@ -37043,7 +37043,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>1104.92</v>
+        <v>1116.94</v>
       </c>
     </row>
     <row r="601">
@@ -37104,7 +37104,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>36.08</v>
+        <v>36.47</v>
       </c>
     </row>
     <row r="602">
@@ -37165,7 +37165,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>1477.81</v>
+        <v>1493.88</v>
       </c>
     </row>
     <row r="603">
@@ -37226,7 +37226,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>8775.84</v>
+        <v>8871.290000000001</v>
       </c>
     </row>
     <row r="604">
@@ -37287,7 +37287,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>360.75</v>
+        <v>364.68</v>
       </c>
     </row>
     <row r="605">
@@ -37348,7 +37348,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>584.51</v>
+        <v>590.87</v>
       </c>
     </row>
     <row r="606">
@@ -37409,7 +37409,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>206.66</v>
+        <v>208.91</v>
       </c>
     </row>
     <row r="607">
@@ -37470,7 +37470,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>485.7</v>
+        <v>490.98</v>
       </c>
     </row>
     <row r="608">
@@ -37527,7 +37527,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>352.28</v>
+        <v>356.12</v>
       </c>
     </row>
     <row r="609">
@@ -37588,7 +37588,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>6668.7</v>
+        <v>6741.23</v>
       </c>
     </row>
     <row r="610">
@@ -37649,7 +37649,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>486.84</v>
+        <v>492.13</v>
       </c>
     </row>
     <row r="611">
@@ -37710,7 +37710,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>1994.15</v>
+        <v>2015.84</v>
       </c>
     </row>
     <row r="612">
@@ -37771,7 +37771,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>130.87</v>
+        <v>132.29</v>
       </c>
     </row>
     <row r="613">
@@ -37832,7 +37832,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>82.16</v>
+        <v>83.05</v>
       </c>
     </row>
     <row r="614">
@@ -37893,7 +37893,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>140.02</v>
+        <v>141.55</v>
       </c>
     </row>
     <row r="615">
@@ -37954,7 +37954,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>337.78</v>
+        <v>341.46</v>
       </c>
     </row>
     <row r="616">
@@ -38015,7 +38015,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>1212.33</v>
+        <v>1225.52</v>
       </c>
     </row>
     <row r="617">
@@ -38076,7 +38076,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>9192.35</v>
+        <v>9292.33</v>
       </c>
     </row>
     <row r="618">
@@ -38137,7 +38137,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>757.98</v>
+        <v>766.22</v>
       </c>
     </row>
     <row r="619">
@@ -38198,7 +38198,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>1392.46</v>
+        <v>1407.6</v>
       </c>
     </row>
     <row r="620">
@@ -38259,7 +38259,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>13258.7</v>
+        <v>13402.9</v>
       </c>
     </row>
     <row r="621">
@@ -38320,7 +38320,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>12073.98</v>
+        <v>12205.31</v>
       </c>
     </row>
     <row r="622">
@@ -38381,7 +38381,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>923.3099999999999</v>
+        <v>933.35</v>
       </c>
     </row>
     <row r="623">
@@ -38442,7 +38442,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>84.45</v>
+        <v>84.72</v>
       </c>
     </row>
     <row r="624">
@@ -38503,7 +38503,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>527.41</v>
+        <v>529.14</v>
       </c>
     </row>
     <row r="625">
@@ -38564,7 +38564,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>7715.85</v>
+        <v>7741.23</v>
       </c>
     </row>
     <row r="626">
@@ -38625,7 +38625,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>1198.02</v>
+        <v>1201.96</v>
       </c>
     </row>
     <row r="627">
@@ -38686,7 +38686,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>4870.02</v>
+        <v>4886.04</v>
       </c>
     </row>
     <row r="628">
@@ -38747,7 +38747,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>5343.75</v>
+        <v>5361.32</v>
       </c>
     </row>
     <row r="629">
@@ -38808,7 +38808,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>124</v>
+        <v>124.41</v>
       </c>
     </row>
     <row r="630">
@@ -38869,7 +38869,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>233.37</v>
+        <v>234.14</v>
       </c>
     </row>
     <row r="631">
@@ -38930,7 +38930,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>138.43</v>
+        <v>138.89</v>
       </c>
     </row>
     <row r="632">
@@ -38991,7 +38991,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>221.29</v>
+        <v>222.02</v>
       </c>
     </row>
     <row r="633">
@@ -39052,7 +39052,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>184.66</v>
+        <v>185.27</v>
       </c>
     </row>
     <row r="634">
@@ -39113,7 +39113,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>237.31</v>
+        <v>238.09</v>
       </c>
     </row>
     <row r="635">
@@ -39174,7 +39174,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>64.59999999999999</v>
+        <v>64.81</v>
       </c>
     </row>
     <row r="636">
@@ -39235,7 +39235,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>1894.95</v>
+        <v>1901.18</v>
       </c>
     </row>
     <row r="637">
@@ -39296,7 +39296,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>6444.29</v>
+        <v>6465.49</v>
       </c>
     </row>
     <row r="638">
@@ -39357,7 +39357,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>1154.14</v>
+        <v>1157.94</v>
       </c>
     </row>
     <row r="639">
@@ -39418,7 +39418,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>531.09</v>
+        <v>532.84</v>
       </c>
     </row>
     <row r="640">
@@ -39479,7 +39479,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>953.67</v>
+        <v>956.8099999999999</v>
       </c>
     </row>
     <row r="641">
@@ -39540,7 +39540,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>158.21</v>
+        <v>158.73</v>
       </c>
     </row>
     <row r="642">
@@ -39601,7 +39601,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>354.06</v>
+        <v>355.23</v>
       </c>
     </row>
     <row r="643">
@@ -39662,7 +39662,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>657</v>
+        <v>659.16</v>
       </c>
     </row>
     <row r="644">
@@ -39723,7 +39723,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>151.6</v>
+        <v>152.09</v>
       </c>
     </row>
     <row r="645">
@@ -39784,7 +39784,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>5249.89</v>
+        <v>5267.16</v>
       </c>
     </row>
     <row r="646">
@@ -39845,7 +39845,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>280.05</v>
+        <v>280.97</v>
       </c>
     </row>
     <row r="647">
@@ -39906,7 +39906,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>670.28</v>
+        <v>672.48</v>
       </c>
     </row>
     <row r="648">
@@ -39967,7 +39967,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>167.57</v>
+        <v>168.12</v>
       </c>
     </row>
     <row r="649">
@@ -40028,7 +40028,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>130.33</v>
+        <v>130.76</v>
       </c>
     </row>
     <row r="650">
@@ -40089,7 +40089,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>913.78</v>
+        <v>916.79</v>
       </c>
     </row>
     <row r="651">
@@ -40150,7 +40150,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>2270.12</v>
+        <v>2277.59</v>
       </c>
     </row>
     <row r="652">
@@ -40211,7 +40211,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>1354.44</v>
+        <v>1358.9</v>
       </c>
     </row>
     <row r="653">
@@ -40272,7 +40272,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>1488.08</v>
+        <v>1492.98</v>
       </c>
     </row>
     <row r="654">
@@ -40333,7 +40333,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>335.14</v>
+        <v>336.24</v>
       </c>
     </row>
     <row r="655">
@@ -40394,7 +40394,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>98.88</v>
+        <v>99.20999999999999</v>
       </c>
     </row>
     <row r="656">
@@ -40455,7 +40455,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>376.83</v>
+        <v>378.07</v>
       </c>
     </row>
     <row r="657">
@@ -40516,7 +40516,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>133.23</v>
+        <v>133.66</v>
       </c>
     </row>
     <row r="658">
@@ -40577,7 +40577,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>74.31</v>
+        <v>74.56</v>
       </c>
     </row>
     <row r="659">
@@ -40638,7 +40638,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>186.2</v>
+        <v>186.82</v>
       </c>
     </row>
     <row r="660">
@@ -40699,7 +40699,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>237.31</v>
+        <v>238.09</v>
       </c>
     </row>
     <row r="661">
@@ -40760,7 +40760,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>1515.96</v>
+        <v>1520.95</v>
       </c>
     </row>
     <row r="662">
@@ -40821,7 +40821,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>180.29</v>
+        <v>180.89</v>
       </c>
     </row>
     <row r="663">
@@ -40882,7 +40882,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>1021.24</v>
+        <v>1024.6</v>
       </c>
     </row>
     <row r="664">
@@ -40943,7 +40943,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>519.14</v>
+        <v>520.85</v>
       </c>
     </row>
     <row r="665">
@@ -41004,7 +41004,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>20.33</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="666">
@@ -41065,7 +41065,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>5309.62</v>
+        <v>5327.08</v>
       </c>
     </row>
     <row r="667">
@@ -41126,7 +41126,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>1173.85</v>
+        <v>1177.71</v>
       </c>
     </row>
     <row r="668">
@@ -41187,7 +41187,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>10652.44</v>
+        <v>10687.48</v>
       </c>
     </row>
     <row r="669">
@@ -41248,7 +41248,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>868.63</v>
+        <v>871.48</v>
       </c>
     </row>
     <row r="670">
@@ -41309,7 +41309,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>974.1799999999999</v>
+        <v>977.39</v>
       </c>
     </row>
     <row r="671">
@@ -41370,7 +41370,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>3055.32</v>
+        <v>3065.37</v>
       </c>
     </row>
     <row r="672">
@@ -41431,7 +41431,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>610.71</v>
+        <v>612.72</v>
       </c>
     </row>
     <row r="673">
@@ -41492,7 +41492,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>86.98</v>
+        <v>87.27</v>
       </c>
     </row>
     <row r="674">
@@ -41553,7 +41553,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>1623.2</v>
+        <v>1628.53</v>
       </c>
     </row>
     <row r="675">
@@ -41614,7 +41614,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>1790.66</v>
+        <v>1796.55</v>
       </c>
     </row>
     <row r="676">
@@ -41675,7 +41675,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>126.67</v>
+        <v>127.09</v>
       </c>
     </row>
     <row r="677">
@@ -41736,7 +41736,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>4056.97</v>
+        <v>4070.32</v>
       </c>
     </row>
     <row r="678">
@@ -41797,7 +41797,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>1809.68</v>
+        <v>1815.63</v>
       </c>
     </row>
     <row r="679">
@@ -41858,7 +41858,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>136.21</v>
+        <v>136.66</v>
       </c>
     </row>
     <row r="680">
@@ -41919,7 +41919,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>116.54</v>
+        <v>116.92</v>
       </c>
     </row>
     <row r="681">
@@ -41980,7 +41980,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>47.71</v>
+        <v>47.87</v>
       </c>
     </row>
     <row r="682">
@@ -42041,7 +42041,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>126.67</v>
+        <v>127.09</v>
       </c>
     </row>
     <row r="683">
@@ -42102,7 +42102,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>216.04</v>
+        <v>216.75</v>
       </c>
     </row>
     <row r="684">
@@ -42163,7 +42163,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>717.59</v>
+        <v>719.95</v>
       </c>
     </row>
     <row r="685">
@@ -42224,7 +42224,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>126.67</v>
+        <v>127.09</v>
       </c>
     </row>
     <row r="686">
@@ -42285,7 +42285,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>213.65</v>
+        <v>214.35</v>
       </c>
     </row>
     <row r="687">
@@ -42346,7 +42346,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>48.56</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="688">
@@ -42407,7 +42407,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>156.65</v>
+        <v>157.16</v>
       </c>
     </row>
     <row r="689">
@@ -42468,7 +42468,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>119.07</v>
+        <v>119.46</v>
       </c>
     </row>
     <row r="690">
@@ -42529,7 +42529,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>1435.35</v>
+        <v>1460.12</v>
       </c>
     </row>
     <row r="691">
@@ -42590,7 +42590,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>3573.95</v>
+        <v>3635.64</v>
       </c>
     </row>
     <row r="692">
@@ -42651,7 +42651,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>115.1</v>
+        <v>117.08</v>
       </c>
     </row>
     <row r="693">
@@ -42712,7 +42712,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>158.22</v>
+        <v>160.95</v>
       </c>
     </row>
     <row r="694">
@@ -42773,7 +42773,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>183.19</v>
+        <v>186.35</v>
       </c>
     </row>
     <row r="695">
@@ -42834,7 +42834,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>138.5</v>
+        <v>140.89</v>
       </c>
     </row>
     <row r="696">
@@ -42895,7 +42895,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>152.23</v>
+        <v>154.86</v>
       </c>
     </row>
     <row r="697">
@@ -42956,7 +42956,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>152.23</v>
+        <v>154.86</v>
       </c>
     </row>
     <row r="698">
@@ -43017,7 +43017,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>8184.14</v>
+        <v>8325.41</v>
       </c>
     </row>
     <row r="699">
@@ -43078,7 +43078,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>37108.97</v>
+        <v>37749.53</v>
       </c>
     </row>
     <row r="700">
@@ -43139,7 +43139,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>7110.78</v>
+        <v>7233.53</v>
       </c>
     </row>
     <row r="701">
@@ -43200,7 +43200,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>1708.47</v>
+        <v>1737.96</v>
       </c>
     </row>
     <row r="702">
@@ -43261,7 +43261,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>1948.36</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="703">
@@ -43322,7 +43322,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>769.35</v>
+        <v>782.63</v>
       </c>
     </row>
     <row r="704">
@@ -43383,7 +43383,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>101.42</v>
+        <v>103.18</v>
       </c>
     </row>
     <row r="705">
@@ -43444,7 +43444,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>266.01</v>
+        <v>270.6</v>
       </c>
     </row>
     <row r="706">
@@ -43505,7 +43505,7 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>266.01</v>
+        <v>270.6</v>
       </c>
     </row>
     <row r="707">
@@ -43566,7 +43566,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>1557.57</v>
+        <v>1584.46</v>
       </c>
     </row>
     <row r="708">
@@ -43627,7 +43627,7 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>161.5</v>
+        <v>164.28</v>
       </c>
     </row>
     <row r="709">
@@ -43688,7 +43688,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>1400.23</v>
+        <v>1424.4</v>
       </c>
     </row>
     <row r="710">
@@ -43749,7 +43749,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>1154.14</v>
+        <v>1174.06</v>
       </c>
     </row>
     <row r="711">
@@ -43810,7 +43810,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>80.79000000000001</v>
+        <v>82.18000000000001</v>
       </c>
     </row>
     <row r="712">
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>276.23</v>
+        <v>281</v>
       </c>
     </row>
     <row r="713">
@@ -43932,7 +43932,7 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>157.57</v>
+        <v>160.29</v>
       </c>
     </row>
     <row r="714">
@@ -43993,7 +43993,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>119.7</v>
+        <v>121.77</v>
       </c>
     </row>
     <row r="715">
@@ -44054,7 +44054,7 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>402.9</v>
+        <v>409.85</v>
       </c>
     </row>
     <row r="716">
@@ -44115,7 +44115,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>266.01</v>
+        <v>270.6</v>
       </c>
     </row>
     <row r="717">
@@ -44176,7 +44176,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>266.01</v>
+        <v>270.6</v>
       </c>
     </row>
     <row r="718">
@@ -44237,7 +44237,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>266.01</v>
+        <v>270.6</v>
       </c>
     </row>
     <row r="719">
@@ -44298,7 +44298,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>974.1799999999999</v>
+        <v>991</v>
       </c>
     </row>
     <row r="720">
@@ -44359,7 +44359,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>1593.36</v>
+        <v>1620.86</v>
       </c>
     </row>
     <row r="721">
@@ -44420,7 +44420,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>165.33</v>
+        <v>168.19</v>
       </c>
     </row>
     <row r="722">
@@ -44481,7 +44481,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>560.09</v>
+        <v>569.76</v>
       </c>
     </row>
     <row r="723">
@@ -44542,7 +44542,7 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>62.18</v>
+        <v>63.25</v>
       </c>
     </row>
     <row r="724">
@@ -44603,7 +44603,7 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>422.23</v>
+        <v>429.52</v>
       </c>
     </row>
     <row r="725">
@@ -44664,7 +44664,7 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>581.97</v>
+        <v>592.01</v>
       </c>
     </row>
     <row r="726">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>1217.09</v>
+        <v>1238.1</v>
       </c>
     </row>
     <row r="727">
@@ -44786,7 +44786,7 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>1406.62</v>
+        <v>1430.9</v>
       </c>
     </row>
     <row r="728">
@@ -44847,7 +44847,7 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>309.81</v>
+        <v>315.15</v>
       </c>
     </row>
     <row r="729">
@@ -44908,7 +44908,7 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>2840.17</v>
+        <v>2889.19</v>
       </c>
     </row>
     <row r="730">
@@ -44969,7 +44969,7 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>1593.28</v>
+        <v>1620.79</v>
       </c>
     </row>
     <row r="731">
@@ -45030,7 +45030,7 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>1688.92</v>
+        <v>1718.08</v>
       </c>
     </row>
     <row r="732">
@@ -45091,7 +45091,7 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>354.06</v>
+        <v>360.17</v>
       </c>
     </row>
     <row r="733">
@@ -45152,7 +45152,7 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>328.63</v>
+        <v>334.3</v>
       </c>
     </row>
     <row r="734">
@@ -45213,7 +45213,7 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>2874.68</v>
+        <v>2924.3</v>
       </c>
     </row>
     <row r="735">
@@ -45274,7 +45274,7 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>575.48</v>
+        <v>585.41</v>
       </c>
     </row>
     <row r="736">
@@ -45335,7 +45335,7 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>431.32</v>
+        <v>438.77</v>
       </c>
     </row>
     <row r="737">
@@ -45396,7 +45396,7 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>1493.74</v>
+        <v>1519.53</v>
       </c>
     </row>
     <row r="738">
@@ -45457,7 +45457,7 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>2225.52</v>
+        <v>2263.94</v>
       </c>
     </row>
     <row r="739">
@@ -45518,7 +45518,7 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>248</v>
+        <v>252.28</v>
       </c>
     </row>
     <row r="740">
@@ -45579,7 +45579,7 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>716.27</v>
+        <v>728.63</v>
       </c>
     </row>
     <row r="741">
@@ -45640,7 +45640,7 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>765.1</v>
+        <v>778.3099999999999</v>
       </c>
     </row>
     <row r="742">
@@ -45701,7 +45701,7 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>538.3200000000001</v>
+        <v>547.61</v>
       </c>
     </row>
     <row r="743">
@@ -45762,7 +45762,7 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>538.3200000000001</v>
+        <v>547.61</v>
       </c>
     </row>
     <row r="744">
@@ -45823,7 +45823,7 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>130.48</v>
+        <v>132.74</v>
       </c>
     </row>
     <row r="745">
@@ -45884,7 +45884,7 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>119.55</v>
+        <v>121.61</v>
       </c>
     </row>
     <row r="746">
@@ -45945,7 +45945,7 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>2125.29</v>
+        <v>2161.98</v>
       </c>
     </row>
     <row r="747">
@@ -46006,7 +46006,7 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>1014.88</v>
+        <v>1032.4</v>
       </c>
     </row>
     <row r="748">
@@ -46067,7 +46067,7 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>553.99</v>
+        <v>563.55</v>
       </c>
     </row>
     <row r="749">
@@ -46128,7 +46128,7 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>5074.4</v>
+        <v>5161.99</v>
       </c>
     </row>
     <row r="750">
@@ -46189,7 +46189,7 @@
         </is>
       </c>
       <c r="M750" s="2" t="n">
-        <v>4201.96</v>
+        <v>4274.49</v>
       </c>
     </row>
     <row r="751">
@@ -46250,7 +46250,7 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>1442.2</v>
+        <v>1467.09</v>
       </c>
     </row>
     <row r="752">
@@ -46311,7 +46311,7 @@
         </is>
       </c>
       <c r="M752" s="2" t="n">
-        <v>438.38</v>
+        <v>445.95</v>
       </c>
     </row>
     <row r="753">
@@ -46372,7 +46372,7 @@
         </is>
       </c>
       <c r="M753" s="2" t="n">
-        <v>762.03</v>
+        <v>775.1799999999999</v>
       </c>
     </row>
     <row r="754">
@@ -46433,7 +46433,7 @@
         </is>
       </c>
       <c r="M754" s="2" t="n">
-        <v>167.46</v>
+        <v>170.35</v>
       </c>
     </row>
     <row r="755">
@@ -46494,7 +46494,7 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>285.88</v>
+        <v>290.82</v>
       </c>
     </row>
     <row r="756">
@@ -46555,7 +46555,7 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>984.22</v>
+        <v>1001.21</v>
       </c>
     </row>
     <row r="757">
@@ -46616,7 +46616,7 @@
         </is>
       </c>
       <c r="M757" s="2" t="n">
-        <v>180.59</v>
+        <v>183.71</v>
       </c>
     </row>
     <row r="758">
@@ -46677,7 +46677,7 @@
         </is>
       </c>
       <c r="M758" s="2" t="n">
-        <v>56.52</v>
+        <v>56.92</v>
       </c>
     </row>
     <row r="759">
@@ -46738,7 +46738,7 @@
         </is>
       </c>
       <c r="M759" s="2" t="n">
-        <v>2280.04</v>
+        <v>2295.84</v>
       </c>
     </row>
     <row r="760">
@@ -46799,7 +46799,7 @@
         </is>
       </c>
       <c r="M760" s="2" t="n">
-        <v>2434.18</v>
+        <v>2451.05</v>
       </c>
     </row>
     <row r="761">
@@ -46860,7 +46860,7 @@
         </is>
       </c>
       <c r="M761" s="2" t="n">
-        <v>132.26</v>
+        <v>133.18</v>
       </c>
     </row>
     <row r="762">
@@ -46921,7 +46921,7 @@
         </is>
       </c>
       <c r="M762" s="2" t="n">
-        <v>1077.2</v>
+        <v>1084.66</v>
       </c>
     </row>
     <row r="763">
@@ -46982,7 +46982,7 @@
         </is>
       </c>
       <c r="M763" s="2" t="n">
-        <v>4476.66</v>
+        <v>4507.67</v>
       </c>
     </row>
     <row r="764">
@@ -47043,7 +47043,7 @@
         </is>
       </c>
       <c r="M764" s="2" t="n">
-        <v>17601.41</v>
+        <v>17723.35</v>
       </c>
     </row>
     <row r="765">
@@ -47104,7 +47104,7 @@
         </is>
       </c>
       <c r="M765" s="2" t="n">
-        <v>1396.67</v>
+        <v>1406.34</v>
       </c>
     </row>
     <row r="766">
@@ -47165,7 +47165,7 @@
         </is>
       </c>
       <c r="M766" s="2" t="n">
-        <v>113.05</v>
+        <v>113.83</v>
       </c>
     </row>
     <row r="767">
@@ -47226,7 +47226,7 @@
         </is>
       </c>
       <c r="M767" s="2" t="n">
-        <v>3732.08</v>
+        <v>3757.93</v>
       </c>
     </row>
     <row r="768">
@@ -47287,7 +47287,7 @@
         </is>
       </c>
       <c r="M768" s="2" t="n">
-        <v>57.57</v>
+        <v>57.97</v>
       </c>
     </row>
     <row r="769">
@@ -47348,7 +47348,7 @@
         </is>
       </c>
       <c r="M769" s="2" t="n">
-        <v>111.41</v>
+        <v>112.18</v>
       </c>
     </row>
     <row r="770">
@@ -47409,7 +47409,7 @@
         </is>
       </c>
       <c r="M770" s="2" t="n">
-        <v>1095.38</v>
+        <v>1102.97</v>
       </c>
     </row>
     <row r="771">
@@ -47470,7 +47470,7 @@
         </is>
       </c>
       <c r="M771" s="2" t="n">
-        <v>395.52</v>
+        <v>398.26</v>
       </c>
     </row>
     <row r="772">
@@ -47531,7 +47531,7 @@
         </is>
       </c>
       <c r="M772" s="2" t="n">
-        <v>395.52</v>
+        <v>398.26</v>
       </c>
     </row>
     <row r="773">
@@ -47592,7 +47592,7 @@
         </is>
       </c>
       <c r="M773" s="2" t="n">
-        <v>111.41</v>
+        <v>112.18</v>
       </c>
     </row>
     <row r="774">
@@ -47653,7 +47653,7 @@
         </is>
       </c>
       <c r="M774" s="2" t="n">
-        <v>111.41</v>
+        <v>112.18</v>
       </c>
     </row>
     <row r="775">
@@ -47714,7 +47714,7 @@
         </is>
       </c>
       <c r="M775" s="2" t="n">
-        <v>53.4</v>
+        <v>53.77</v>
       </c>
     </row>
     <row r="776">
@@ -47775,7 +47775,7 @@
         </is>
       </c>
       <c r="M776" s="2" t="n">
-        <v>885.16</v>
+        <v>891.29</v>
       </c>
     </row>
     <row r="777">
@@ -47836,7 +47836,7 @@
         </is>
       </c>
       <c r="M777" s="2" t="n">
-        <v>871.6799999999999</v>
+        <v>877.72</v>
       </c>
     </row>
     <row r="778">
@@ -47897,7 +47897,7 @@
         </is>
       </c>
       <c r="M778" s="2" t="n">
-        <v>125.07</v>
+        <v>125.93</v>
       </c>
     </row>
     <row r="779">
@@ -47958,7 +47958,7 @@
         </is>
       </c>
       <c r="M779" s="2" t="n">
-        <v>441.31</v>
+        <v>444.36</v>
       </c>
     </row>
     <row r="780">
@@ -48019,7 +48019,7 @@
         </is>
       </c>
       <c r="M780" s="2" t="n">
-        <v>724.41</v>
+        <v>729.42</v>
       </c>
     </row>
     <row r="781">
@@ -48080,7 +48080,7 @@
         </is>
       </c>
       <c r="M781" s="2" t="n">
-        <v>981.8099999999999</v>
+        <v>986.39</v>
       </c>
     </row>
     <row r="782">
@@ -48141,7 +48141,7 @@
         </is>
       </c>
       <c r="M782" s="2" t="n">
-        <v>1615.79</v>
+        <v>1623.32</v>
       </c>
     </row>
     <row r="783">
@@ -48202,7 +48202,7 @@
         </is>
       </c>
       <c r="M783" s="2" t="n">
-        <v>1071.85</v>
+        <v>1076.85</v>
       </c>
     </row>
     <row r="784">
@@ -48263,7 +48263,7 @@
         </is>
       </c>
       <c r="M784" s="2" t="n">
-        <v>506.68</v>
+        <v>509.04</v>
       </c>
     </row>
     <row r="785">
@@ -48324,7 +48324,7 @@
         </is>
       </c>
       <c r="M785" s="2" t="n">
-        <v>1096.78</v>
+        <v>1101.89</v>
       </c>
     </row>
     <row r="786">
@@ -48385,7 +48385,7 @@
         </is>
       </c>
       <c r="M786" s="2" t="n">
-        <v>2939.28</v>
+        <v>2952.97</v>
       </c>
     </row>
     <row r="787">
@@ -48446,7 +48446,7 @@
         </is>
       </c>
       <c r="M787" s="2" t="n">
-        <v>1196.49</v>
+        <v>1202.06</v>
       </c>
     </row>
     <row r="788">
@@ -48507,7 +48507,7 @@
         </is>
       </c>
       <c r="M788" s="2" t="n">
-        <v>1592.27</v>
+        <v>1599.68</v>
       </c>
     </row>
     <row r="789">
@@ -48568,7 +48568,7 @@
         </is>
       </c>
       <c r="M789" s="2" t="n">
-        <v>292.86</v>
+        <v>294.22</v>
       </c>
     </row>
     <row r="790">
@@ -48629,7 +48629,7 @@
         </is>
       </c>
       <c r="M790" s="2" t="n">
-        <v>217.47</v>
+        <v>218.49</v>
       </c>
     </row>
     <row r="791">
@@ -48690,7 +48690,7 @@
         </is>
       </c>
       <c r="M791" s="2" t="n">
-        <v>817.24</v>
+        <v>821.05</v>
       </c>
     </row>
     <row r="792">
@@ -48751,7 +48751,7 @@
         </is>
       </c>
       <c r="M792" s="2" t="n">
-        <v>460.42</v>
+        <v>462.57</v>
       </c>
     </row>
     <row r="793">
@@ -48812,7 +48812,7 @@
         </is>
       </c>
       <c r="M793" s="2" t="n">
-        <v>829.2</v>
+        <v>833.0599999999999</v>
       </c>
     </row>
     <row r="794">
@@ -48873,7 +48873,7 @@
         </is>
       </c>
       <c r="M794" s="2" t="n">
-        <v>479.46</v>
+        <v>481.69</v>
       </c>
     </row>
     <row r="795">
@@ -48934,7 +48934,7 @@
         </is>
       </c>
       <c r="M795" s="2" t="n">
-        <v>110.07</v>
+        <v>110.58</v>
       </c>
     </row>
     <row r="796">
@@ -48995,7 +48995,7 @@
         </is>
       </c>
       <c r="M796" s="2" t="n">
-        <v>2276.94</v>
+        <v>2287.55</v>
       </c>
     </row>
     <row r="797">
@@ -49056,7 +49056,7 @@
         </is>
       </c>
       <c r="M797" s="2" t="n">
-        <v>1106.98</v>
+        <v>1112.14</v>
       </c>
     </row>
     <row r="798">
@@ -49117,7 +49117,7 @@
         </is>
       </c>
       <c r="M798" s="2" t="n">
-        <v>2151.04</v>
+        <v>2161.05</v>
       </c>
     </row>
     <row r="799">
@@ -49178,7 +49178,7 @@
         </is>
       </c>
       <c r="M799" s="2" t="n">
-        <v>1114.08</v>
+        <v>1119.27</v>
       </c>
     </row>
     <row r="800">
@@ -49239,7 +49239,7 @@
         </is>
       </c>
       <c r="M800" s="2" t="n">
-        <v>178.39</v>
+        <v>179.22</v>
       </c>
     </row>
     <row r="801">
@@ -49300,7 +49300,7 @@
         </is>
       </c>
       <c r="M801" s="2" t="n">
-        <v>3084.62</v>
+        <v>3098.99</v>
       </c>
     </row>
     <row r="802">
@@ -49361,7 +49361,7 @@
         </is>
       </c>
       <c r="M802" s="2" t="n">
-        <v>567.98</v>
+        <v>570.62</v>
       </c>
     </row>
     <row r="803">
@@ -49422,7 +49422,7 @@
         </is>
       </c>
       <c r="M803" s="2" t="n">
-        <v>398.83</v>
+        <v>400.69</v>
       </c>
     </row>
     <row r="804">
@@ -49483,7 +49483,7 @@
         </is>
       </c>
       <c r="M804" s="2" t="n">
-        <v>564.9400000000001</v>
+        <v>567.5700000000001</v>
       </c>
     </row>
     <row r="805">
@@ -49544,7 +49544,7 @@
         </is>
       </c>
       <c r="M805" s="2" t="n">
-        <v>139.58</v>
+        <v>140.23</v>
       </c>
     </row>
     <row r="806">
@@ -49605,7 +49605,7 @@
         </is>
       </c>
       <c r="M806" s="2" t="n">
-        <v>671.5</v>
+        <v>674.63</v>
       </c>
     </row>
     <row r="807">
@@ -49666,7 +49666,7 @@
         </is>
       </c>
       <c r="M807" s="2" t="n">
-        <v>152.23</v>
+        <v>152.94</v>
       </c>
     </row>
     <row r="808">
@@ -49723,7 +49723,7 @@
         </is>
       </c>
       <c r="M808" s="2" t="n">
-        <v>442.58</v>
+        <v>444.64</v>
       </c>
     </row>
     <row r="809">
@@ -49784,7 +49784,7 @@
         </is>
       </c>
       <c r="M809" s="2" t="n">
-        <v>7054.71</v>
+        <v>7087.56</v>
       </c>
     </row>
     <row r="810">
@@ -49845,7 +49845,7 @@
         </is>
       </c>
       <c r="M810" s="2" t="n">
-        <v>2652.93</v>
+        <v>2665.29</v>
       </c>
     </row>
     <row r="811">
@@ -49906,7 +49906,7 @@
         </is>
       </c>
       <c r="M811" s="2" t="n">
-        <v>1532.64</v>
+        <v>1539.77</v>
       </c>
     </row>
     <row r="812">
@@ -49967,7 +49967,7 @@
         </is>
       </c>
       <c r="M812" s="2" t="n">
-        <v>447.56</v>
+        <v>449.65</v>
       </c>
     </row>
     <row r="813">
@@ -50028,7 +50028,7 @@
         </is>
       </c>
       <c r="M813" s="2" t="n">
-        <v>2562.38</v>
+        <v>2574.31</v>
       </c>
     </row>
     <row r="814">
@@ -50089,7 +50089,7 @@
         </is>
       </c>
       <c r="M814" s="2" t="n">
-        <v>88.39</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="815">
@@ -50150,7 +50150,7 @@
         </is>
       </c>
       <c r="M815" s="2" t="n">
-        <v>75.02</v>
+        <v>75.37</v>
       </c>
     </row>
     <row r="816">
@@ -50211,7 +50211,7 @@
         </is>
       </c>
       <c r="M816" s="2" t="n">
-        <v>337.78</v>
+        <v>339.36</v>
       </c>
     </row>
     <row r="817">
@@ -50272,7 +50272,7 @@
         </is>
       </c>
       <c r="M817" s="2" t="n">
-        <v>399.34</v>
+        <v>401.2</v>
       </c>
     </row>
     <row r="818">
@@ -50333,7 +50333,7 @@
         </is>
       </c>
       <c r="M818" s="2" t="n">
-        <v>118.66</v>
+        <v>119.21</v>
       </c>
     </row>
     <row r="819">
@@ -50394,7 +50394,7 @@
         </is>
       </c>
       <c r="M819" s="2" t="n">
-        <v>168.65</v>
+        <v>169.44</v>
       </c>
     </row>
     <row r="820">
@@ -50455,7 +50455,7 @@
         </is>
       </c>
       <c r="M820" s="2" t="n">
-        <v>83.56</v>
+        <v>83.94</v>
       </c>
     </row>
     <row r="821">
@@ -50516,7 +50516,7 @@
         </is>
       </c>
       <c r="M821" s="2" t="n">
-        <v>165.78</v>
+        <v>166.55</v>
       </c>
     </row>
     <row r="822">
@@ -50577,7 +50577,7 @@
         </is>
       </c>
       <c r="M822" s="2" t="n">
-        <v>4564.61</v>
+        <v>4585.87</v>
       </c>
     </row>
     <row r="823">
@@ -50638,7 +50638,7 @@
         </is>
       </c>
       <c r="M823" s="2" t="n">
-        <v>13404.29</v>
+        <v>13466.72</v>
       </c>
     </row>
     <row r="824">
@@ -50699,7 +50699,7 @@
         </is>
       </c>
       <c r="M824" s="2" t="n">
-        <v>1704.82</v>
+        <v>1712.76</v>
       </c>
     </row>
     <row r="825">
@@ -50760,7 +50760,7 @@
         </is>
       </c>
       <c r="M825" s="2" t="n">
-        <v>538.6</v>
+        <v>541.11</v>
       </c>
     </row>
     <row r="826">
@@ -50821,7 +50821,7 @@
         </is>
       </c>
       <c r="M826" s="2" t="n">
-        <v>844.46</v>
+        <v>848.39</v>
       </c>
     </row>
     <row r="827">
@@ -50882,7 +50882,7 @@
         </is>
       </c>
       <c r="M827" s="2" t="n">
-        <v>1155.63</v>
+        <v>1161.02</v>
       </c>
     </row>
     <row r="828">
@@ -50943,7 +50943,7 @@
         </is>
       </c>
       <c r="M828" s="2" t="n">
-        <v>9291</v>
+        <v>9334.27</v>
       </c>
     </row>
     <row r="829">
@@ -51004,7 +51004,7 @@
         </is>
       </c>
       <c r="M829" s="2" t="n">
-        <v>2400.61</v>
+        <v>2417.92</v>
       </c>
     </row>
     <row r="830">
@@ -51065,7 +51065,7 @@
         </is>
       </c>
       <c r="M830" s="2" t="n">
-        <v>267.38</v>
+        <v>269.31</v>
       </c>
     </row>
     <row r="831">
@@ -51126,7 +51126,7 @@
         </is>
       </c>
       <c r="M831" s="2" t="n">
-        <v>229.56</v>
+        <v>231.21</v>
       </c>
     </row>
     <row r="832">
@@ -51187,7 +51187,7 @@
         </is>
       </c>
       <c r="M832" s="2" t="n">
-        <v>705.58</v>
+        <v>710.67</v>
       </c>
     </row>
     <row r="833">
@@ -51248,7 +51248,7 @@
         </is>
       </c>
       <c r="M833" s="2" t="n">
-        <v>213.28</v>
+        <v>214.82</v>
       </c>
     </row>
     <row r="834">
@@ -51309,7 +51309,7 @@
         </is>
       </c>
       <c r="M834" s="2" t="n">
-        <v>139.32</v>
+        <v>140.33</v>
       </c>
     </row>
     <row r="835">
@@ -51370,7 +51370,7 @@
         </is>
       </c>
       <c r="M835" s="2" t="n">
-        <v>2454.53</v>
+        <v>2472.23</v>
       </c>
     </row>
     <row r="836">
@@ -51431,7 +51431,7 @@
         </is>
       </c>
       <c r="M836" s="2" t="n">
-        <v>14460.84</v>
+        <v>14565.09</v>
       </c>
     </row>
     <row r="837">
@@ -51492,7 +51492,7 @@
         </is>
       </c>
       <c r="M837" s="2" t="n">
-        <v>979.27</v>
+        <v>986.33</v>
       </c>
     </row>
     <row r="838">
@@ -51553,7 +51553,7 @@
         </is>
       </c>
       <c r="M838" s="2" t="n">
-        <v>108.23</v>
+        <v>109.01</v>
       </c>
     </row>
     <row r="839">
@@ -51614,7 +51614,7 @@
         </is>
       </c>
       <c r="M839" s="2" t="n">
-        <v>790.3</v>
+        <v>796</v>
       </c>
     </row>
     <row r="840">
@@ -51675,7 +51675,7 @@
         </is>
       </c>
       <c r="M840" s="2" t="n">
-        <v>107.55</v>
+        <v>108.33</v>
       </c>
     </row>
     <row r="841">
@@ -51736,7 +51736,7 @@
         </is>
       </c>
       <c r="M841" s="2" t="n">
-        <v>217.47</v>
+        <v>219.04</v>
       </c>
     </row>
     <row r="842">
@@ -51797,7 +51797,7 @@
         </is>
       </c>
       <c r="M842" s="2" t="n">
-        <v>1540.85</v>
+        <v>1551.96</v>
       </c>
     </row>
     <row r="843">
@@ -51858,7 +51858,7 @@
         </is>
       </c>
       <c r="M843" s="2" t="n">
-        <v>2024.16</v>
+        <v>2038.76</v>
       </c>
     </row>
     <row r="844">
@@ -51919,7 +51919,7 @@
         </is>
       </c>
       <c r="M844" s="2" t="n">
-        <v>9415.610000000001</v>
+        <v>9483.49</v>
       </c>
     </row>
     <row r="845">
@@ -51980,7 +51980,7 @@
         </is>
       </c>
       <c r="M845" s="2" t="n">
-        <v>226.38</v>
+        <v>228.01</v>
       </c>
     </row>
     <row r="846">
@@ -52041,7 +52041,7 @@
         </is>
       </c>
       <c r="M846" s="2" t="n">
-        <v>6970.86</v>
+        <v>7021.12</v>
       </c>
     </row>
     <row r="847">
@@ -52102,7 +52102,7 @@
         </is>
       </c>
       <c r="M847" s="2" t="n">
-        <v>275.47</v>
+        <v>277.45</v>
       </c>
     </row>
     <row r="848">
@@ -52163,7 +52163,7 @@
         </is>
       </c>
       <c r="M848" s="2" t="n">
-        <v>663.36</v>
+        <v>668.14</v>
       </c>
     </row>
     <row r="849">
@@ -52224,7 +52224,7 @@
         </is>
       </c>
       <c r="M849" s="2" t="n">
-        <v>149.73</v>
+        <v>150.81</v>
       </c>
     </row>
     <row r="850">
@@ -52285,7 +52285,7 @@
         </is>
       </c>
       <c r="M850" s="2" t="n">
-        <v>512.78</v>
+        <v>516.48</v>
       </c>
     </row>
     <row r="851">
@@ -52346,7 +52346,7 @@
         </is>
       </c>
       <c r="M851" s="2" t="n">
-        <v>93.09</v>
+        <v>93.77</v>
       </c>
     </row>
     <row r="852">
@@ -52407,7 +52407,7 @@
         </is>
       </c>
       <c r="M852" s="2" t="n">
-        <v>213.34</v>
+        <v>214.88</v>
       </c>
     </row>
     <row r="853">
@@ -52468,7 +52468,7 @@
         </is>
       </c>
       <c r="M853" s="2" t="n">
-        <v>517.49</v>
+        <v>521.22</v>
       </c>
     </row>
     <row r="854">
@@ -52529,7 +52529,7 @@
         </is>
       </c>
       <c r="M854" s="2" t="n">
-        <v>73.7</v>
+        <v>74.23</v>
       </c>
     </row>
     <row r="855">
@@ -52590,7 +52590,7 @@
         </is>
       </c>
       <c r="M855" s="2" t="n">
-        <v>409.56</v>
+        <v>412.52</v>
       </c>
     </row>
     <row r="856">
@@ -52651,7 +52651,7 @@
         </is>
       </c>
       <c r="M856" s="2" t="n">
-        <v>181.61</v>
+        <v>182.92</v>
       </c>
     </row>
     <row r="857">
@@ -52712,7 +52712,7 @@
         </is>
       </c>
       <c r="M857" s="2" t="n">
-        <v>995.04</v>
+        <v>1002.21</v>
       </c>
     </row>
     <row r="858">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="M858" s="2" t="n">
-        <v>1739.79</v>
+        <v>1752.34</v>
       </c>
     </row>
     <row r="859">
@@ -52834,7 +52834,7 @@
         </is>
       </c>
       <c r="M859" s="2" t="n">
-        <v>4442.88</v>
+        <v>4474.91</v>
       </c>
     </row>
     <row r="860">
@@ -52895,7 +52895,7 @@
         </is>
       </c>
       <c r="M860" s="2" t="n">
-        <v>9018.66</v>
+        <v>9083.68</v>
       </c>
     </row>
     <row r="861">
@@ -52956,7 +52956,7 @@
         </is>
       </c>
       <c r="M861" s="2" t="n">
-        <v>717.79</v>
+        <v>722.97</v>
       </c>
     </row>
     <row r="862">
@@ -53017,7 +53017,7 @@
         </is>
       </c>
       <c r="M862" s="2" t="n">
-        <v>139.77</v>
+        <v>140.78</v>
       </c>
     </row>
     <row r="863">
@@ -53078,7 +53078,7 @@
         </is>
       </c>
       <c r="M863" s="2" t="n">
-        <v>446.32</v>
+        <v>449.54</v>
       </c>
     </row>
     <row r="864">
@@ -53139,7 +53139,7 @@
         </is>
       </c>
       <c r="M864" s="2" t="n">
-        <v>6361.41</v>
+        <v>6407.27</v>
       </c>
     </row>
     <row r="865">
@@ -53200,7 +53200,7 @@
         </is>
       </c>
       <c r="M865" s="2" t="n">
-        <v>162.28</v>
+        <v>163.45</v>
       </c>
     </row>
     <row r="866">
@@ -53261,7 +53261,7 @@
         </is>
       </c>
       <c r="M866" s="2" t="n">
-        <v>3377.84</v>
+        <v>3402.2</v>
       </c>
     </row>
     <row r="867">
@@ -53322,7 +53322,7 @@
         </is>
       </c>
       <c r="M867" s="2" t="n">
-        <v>266.91</v>
+        <v>268.84</v>
       </c>
     </row>
     <row r="868">
@@ -53383,7 +53383,7 @@
         </is>
       </c>
       <c r="M868" s="2" t="n">
-        <v>880.0700000000001</v>
+        <v>886.42</v>
       </c>
     </row>
     <row r="869">
@@ -53444,7 +53444,7 @@
         </is>
       </c>
       <c r="M869" s="2" t="n">
-        <v>422.83</v>
+        <v>425.88</v>
       </c>
     </row>
     <row r="870">
@@ -53505,7 +53505,7 @@
         </is>
       </c>
       <c r="M870" s="2" t="n">
-        <v>601.17</v>
+        <v>605.5</v>
       </c>
     </row>
     <row r="871">
@@ -53566,7 +53566,7 @@
         </is>
       </c>
       <c r="M871" s="2" t="n">
-        <v>1597.4</v>
+        <v>1608.92</v>
       </c>
     </row>
     <row r="872">
@@ -53627,7 +53627,7 @@
         </is>
       </c>
       <c r="M872" s="2" t="n">
-        <v>147.78</v>
+        <v>148.85</v>
       </c>
     </row>
     <row r="873">
@@ -53688,7 +53688,7 @@
         </is>
       </c>
       <c r="M873" s="2" t="n">
-        <v>1990.33</v>
+        <v>2004.68</v>
       </c>
     </row>
     <row r="874">
@@ -53749,7 +53749,7 @@
         </is>
       </c>
       <c r="M874" s="2" t="n">
-        <v>692.48</v>
+        <v>697.48</v>
       </c>
     </row>
     <row r="875">
@@ -53810,7 +53810,7 @@
         </is>
       </c>
       <c r="M875" s="2" t="n">
-        <v>2563.91</v>
+        <v>2582.39</v>
       </c>
     </row>
     <row r="876">
@@ -53871,7 +53871,7 @@
         </is>
       </c>
       <c r="M876" s="2" t="n">
-        <v>938.78</v>
+        <v>945.55</v>
       </c>
     </row>
     <row r="877">
@@ -53932,7 +53932,7 @@
         </is>
       </c>
       <c r="M877" s="2" t="n">
-        <v>8666.530000000001</v>
+        <v>8729.02</v>
       </c>
     </row>
     <row r="878">
@@ -53993,7 +53993,7 @@
         </is>
       </c>
       <c r="M878" s="2" t="n">
-        <v>952.75</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="879">
@@ -54054,7 +54054,7 @@
         </is>
       </c>
       <c r="M879" s="2" t="n">
-        <v>1558.25</v>
+        <v>1569.48</v>
       </c>
     </row>
     <row r="880">
@@ -54115,7 +54115,7 @@
         </is>
       </c>
       <c r="M880" s="2" t="n">
-        <v>248.76</v>
+        <v>250.55</v>
       </c>
     </row>
     <row r="881">
@@ -54176,7 +54176,7 @@
         </is>
       </c>
       <c r="M881" s="2" t="n">
-        <v>128.72</v>
+        <v>129.64</v>
       </c>
     </row>
     <row r="882">
@@ -54237,7 +54237,7 @@
         </is>
       </c>
       <c r="M882" s="2" t="n">
-        <v>440.23</v>
+        <v>443.4</v>
       </c>
     </row>
     <row r="883">
@@ -54298,7 +54298,7 @@
         </is>
       </c>
       <c r="M883" s="2" t="n">
-        <v>248.76</v>
+        <v>250.55</v>
       </c>
     </row>
     <row r="884">
@@ -54359,7 +54359,7 @@
         </is>
       </c>
       <c r="M884" s="2" t="n">
-        <v>1069.11</v>
+        <v>1076.82</v>
       </c>
     </row>
     <row r="885">
@@ -54420,7 +54420,7 @@
         </is>
       </c>
       <c r="M885" s="2" t="n">
-        <v>465.47</v>
+        <v>468.83</v>
       </c>
     </row>
     <row r="886">
@@ -54481,7 +54481,7 @@
         </is>
       </c>
       <c r="M886" s="2" t="n">
-        <v>248.76</v>
+        <v>250.55</v>
       </c>
     </row>
     <row r="887">
@@ -54542,7 +54542,7 @@
         </is>
       </c>
       <c r="M887" s="2" t="n">
-        <v>96.97</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="888">
@@ -54603,7 +54603,7 @@
         </is>
       </c>
       <c r="M888" s="2" t="n">
-        <v>561.96</v>
+        <v>560.96</v>
       </c>
     </row>
     <row r="889">
@@ -54664,7 +54664,7 @@
         </is>
       </c>
       <c r="M889" s="2" t="n">
-        <v>1249.52</v>
+        <v>1247.31</v>
       </c>
     </row>
     <row r="890">
@@ -54725,7 +54725,7 @@
         </is>
       </c>
       <c r="M890" s="2" t="n">
-        <v>247.81</v>
+        <v>247.37</v>
       </c>
     </row>
     <row r="891">
@@ -54786,7 +54786,7 @@
         </is>
       </c>
       <c r="M891" s="2" t="n">
-        <v>2599.52</v>
+        <v>2594.9</v>
       </c>
     </row>
     <row r="892">
@@ -54847,7 +54847,7 @@
         </is>
       </c>
       <c r="M892" s="2" t="n">
-        <v>124.38</v>
+        <v>124.16</v>
       </c>
     </row>
     <row r="893">
@@ -54908,7 +54908,7 @@
         </is>
       </c>
       <c r="M893" s="2" t="n">
-        <v>1679.39</v>
+        <v>1676.41</v>
       </c>
     </row>
     <row r="894">
@@ -54969,7 +54969,7 @@
         </is>
       </c>
       <c r="M894" s="2" t="n">
-        <v>275.47</v>
+        <v>274.98</v>
       </c>
     </row>
     <row r="895">
@@ -55030,7 +55030,7 @@
         </is>
       </c>
       <c r="M895" s="2" t="n">
-        <v>1860.61</v>
+        <v>1857.31</v>
       </c>
     </row>
     <row r="896">
@@ -55091,7 +55091,7 @@
         </is>
       </c>
       <c r="M896" s="2" t="n">
-        <v>790.12</v>
+        <v>788.72</v>
       </c>
     </row>
     <row r="897">
@@ -55152,7 +55152,7 @@
         </is>
       </c>
       <c r="M897" s="2" t="n">
-        <v>111.41</v>
+        <v>111.21</v>
       </c>
     </row>
     <row r="898">
@@ -55213,7 +55213,7 @@
         </is>
       </c>
       <c r="M898" s="2" t="n">
-        <v>1036.5</v>
+        <v>1034.66</v>
       </c>
     </row>
     <row r="899">
@@ -55274,7 +55274,7 @@
         </is>
       </c>
       <c r="M899" s="2" t="n">
-        <v>1180.46</v>
+        <v>1178.37</v>
       </c>
     </row>
     <row r="900">
@@ -55335,7 +55335,7 @@
         </is>
       </c>
       <c r="M900" s="2" t="n">
-        <v>579.17</v>
+        <v>578.14</v>
       </c>
     </row>
     <row r="901">
@@ -55396,7 +55396,7 @@
         </is>
       </c>
       <c r="M901" s="2" t="n">
-        <v>1990.08</v>
+        <v>1986.55</v>
       </c>
     </row>
     <row r="902">
@@ -55457,7 +55457,7 @@
         </is>
       </c>
       <c r="M902" s="2" t="n">
-        <v>32304.7</v>
+        <v>32247.4</v>
       </c>
     </row>
     <row r="903">
@@ -55518,7 +55518,7 @@
         </is>
       </c>
       <c r="M903" s="2" t="n">
-        <v>683.71</v>
+        <v>682.5</v>
       </c>
     </row>
     <row r="904">
@@ -55579,7 +55579,7 @@
         </is>
       </c>
       <c r="M904" s="2" t="n">
-        <v>29792.18</v>
+        <v>29739.34</v>
       </c>
     </row>
     <row r="905">
@@ -55640,7 +55640,7 @@
         </is>
       </c>
       <c r="M905" s="2" t="n">
-        <v>1610.64</v>
+        <v>1607.79</v>
       </c>
     </row>
     <row r="906">
@@ -55701,7 +55701,7 @@
         </is>
       </c>
       <c r="M906" s="2" t="n">
-        <v>5127.81</v>
+        <v>5118.72</v>
       </c>
     </row>
     <row r="907">
@@ -55762,7 +55762,7 @@
         </is>
       </c>
       <c r="M907" s="2" t="n">
-        <v>69.59</v>
+        <v>69.47</v>
       </c>
     </row>
     <row r="908">
@@ -55823,7 +55823,7 @@
         </is>
       </c>
       <c r="M908" s="2" t="n">
-        <v>3772.86</v>
+        <v>3766.17</v>
       </c>
     </row>
     <row r="909">
@@ -55884,7 +55884,7 @@
         </is>
       </c>
       <c r="M909" s="2" t="n">
-        <v>34277.19</v>
+        <v>34216.39</v>
       </c>
     </row>
     <row r="910">
@@ -55945,7 +55945,7 @@
         </is>
       </c>
       <c r="M910" s="2" t="n">
-        <v>6246.73</v>
+        <v>6235.65</v>
       </c>
     </row>
     <row r="911">
@@ -56006,7 +56006,7 @@
         </is>
       </c>
       <c r="M911" s="2" t="n">
-        <v>383.57</v>
+        <v>382.89</v>
       </c>
     </row>
     <row r="912">
@@ -56067,7 +56067,7 @@
         </is>
       </c>
       <c r="M912" s="2" t="n">
-        <v>469.29</v>
+        <v>468.45</v>
       </c>
     </row>
     <row r="913">
@@ -56128,7 +56128,7 @@
         </is>
       </c>
       <c r="M913" s="2" t="n">
-        <v>1936.51</v>
+        <v>1933.08</v>
       </c>
     </row>
     <row r="914">
@@ -56189,7 +56189,7 @@
         </is>
       </c>
       <c r="M914" s="2" t="n">
-        <v>381.44</v>
+        <v>380.77</v>
       </c>
     </row>
     <row r="915">
@@ -56250,7 +56250,7 @@
         </is>
       </c>
       <c r="M915" s="2" t="n">
-        <v>202.85</v>
+        <v>202.49</v>
       </c>
     </row>
     <row r="916">
@@ -56311,7 +56311,7 @@
         </is>
       </c>
       <c r="M916" s="2" t="n">
-        <v>92.40000000000001</v>
+        <v>92.23999999999999</v>
       </c>
     </row>
     <row r="917">
@@ -56372,7 +56372,7 @@
         </is>
       </c>
       <c r="M917" s="2" t="n">
-        <v>514.12</v>
+        <v>513.2</v>
       </c>
     </row>
     <row r="918">
@@ -56433,7 +56433,7 @@
         </is>
       </c>
       <c r="M918" s="2" t="n">
-        <v>528.04</v>
+        <v>527.11</v>
       </c>
     </row>
     <row r="919">
@@ -56494,7 +56494,7 @@
         </is>
       </c>
       <c r="M919" s="2" t="n">
-        <v>227.65</v>
+        <v>227.24</v>
       </c>
     </row>
     <row r="920">
@@ -56555,7 +56555,7 @@
         </is>
       </c>
       <c r="M920" s="2" t="n">
-        <v>387.89</v>
+        <v>387.2</v>
       </c>
     </row>
     <row r="921">
@@ -56616,7 +56616,7 @@
         </is>
       </c>
       <c r="M921" s="2" t="n">
-        <v>2193.86</v>
+        <v>2189.97</v>
       </c>
     </row>
     <row r="922">
@@ -56677,7 +56677,7 @@
         </is>
       </c>
       <c r="M922" s="2" t="n">
-        <v>183.84</v>
+        <v>183.51</v>
       </c>
     </row>
     <row r="923">
@@ -56738,7 +56738,7 @@
         </is>
       </c>
       <c r="M923" s="2" t="n">
-        <v>238.84</v>
+        <v>238.42</v>
       </c>
     </row>
     <row r="924">
@@ -56799,7 +56799,7 @@
         </is>
       </c>
       <c r="M924" s="2" t="n">
-        <v>222.82</v>
+        <v>222.42</v>
       </c>
     </row>
     <row r="925">
@@ -56860,7 +56860,7 @@
         </is>
       </c>
       <c r="M925" s="2" t="n">
-        <v>543.3</v>
+        <v>542.34</v>
       </c>
     </row>
     <row r="926">
@@ -56921,7 +56921,7 @@
         </is>
       </c>
       <c r="M926" s="2" t="n">
-        <v>65.88</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="927">
@@ -56982,7 +56982,7 @@
         </is>
       </c>
       <c r="M927" s="2" t="n">
-        <v>306.06</v>
+        <v>305.52</v>
       </c>
     </row>
     <row r="928">
@@ -57043,7 +57043,7 @@
         </is>
       </c>
       <c r="M928" s="2" t="n">
-        <v>230.83</v>
+        <v>230.42</v>
       </c>
     </row>
     <row r="929">
@@ -57104,7 +57104,7 @@
         </is>
       </c>
       <c r="M929" s="2" t="n">
-        <v>289.33</v>
+        <v>288.82</v>
       </c>
     </row>
     <row r="930">
@@ -57165,7 +57165,7 @@
         </is>
       </c>
       <c r="M930" s="2" t="n">
-        <v>1739.79</v>
+        <v>1736.71</v>
       </c>
     </row>
     <row r="931">
@@ -57226,7 +57226,7 @@
         </is>
       </c>
       <c r="M931" s="2" t="n">
-        <v>1556.34</v>
+        <v>1553.58</v>
       </c>
     </row>
     <row r="932">
@@ -57287,7 +57287,7 @@
         </is>
       </c>
       <c r="M932" s="2" t="n">
-        <v>193.95</v>
+        <v>193.6</v>
       </c>
     </row>
     <row r="933">
@@ -57348,7 +57348,7 @@
         </is>
       </c>
       <c r="M933" s="2" t="n">
-        <v>4400.35</v>
+        <v>4392.55</v>
       </c>
     </row>
     <row r="934">
@@ -57409,7 +57409,7 @@
         </is>
       </c>
       <c r="M934" s="2" t="n">
-        <v>2434.18</v>
+        <v>2424.15</v>
       </c>
     </row>
     <row r="935">
@@ -57470,7 +57470,7 @@
         </is>
       </c>
       <c r="M935" s="2" t="n">
-        <v>486.84</v>
+        <v>484.83</v>
       </c>
     </row>
     <row r="936">
@@ -57531,7 +57531,7 @@
         </is>
       </c>
       <c r="M936" s="2" t="n">
-        <v>620.09</v>
+        <v>617.54</v>
       </c>
     </row>
     <row r="937">
@@ -57592,7 +57592,7 @@
         </is>
       </c>
       <c r="M937" s="2" t="n">
-        <v>517.49</v>
+        <v>515.35</v>
       </c>
     </row>
     <row r="938">
@@ -57653,7 +57653,7 @@
         </is>
       </c>
       <c r="M938" s="2" t="n">
-        <v>272.42</v>
+        <v>271.3</v>
       </c>
     </row>
     <row r="939">
@@ -57714,7 +57714,7 @@
         </is>
       </c>
       <c r="M939" s="2" t="n">
-        <v>538.98</v>
+        <v>536.76</v>
       </c>
     </row>
     <row r="940">
@@ -57775,7 +57775,7 @@
         </is>
       </c>
       <c r="M940" s="2" t="n">
-        <v>3534.27</v>
+        <v>3519.71</v>
       </c>
     </row>
     <row r="941">
@@ -57836,7 +57836,7 @@
         </is>
       </c>
       <c r="M941" s="2" t="n">
-        <v>1923.64</v>
+        <v>1915.71</v>
       </c>
     </row>
     <row r="942">
@@ -57897,7 +57897,7 @@
         </is>
       </c>
       <c r="M942" s="2" t="n">
-        <v>217.47</v>
+        <v>216.58</v>
       </c>
     </row>
     <row r="943">
@@ -57958,7 +57958,7 @@
         </is>
       </c>
       <c r="M943" s="2" t="n">
-        <v>928.4</v>
+        <v>924.5700000000001</v>
       </c>
     </row>
     <row r="944">
@@ -58019,7 +58019,7 @@
         </is>
       </c>
       <c r="M944" s="2" t="n">
-        <v>891.26</v>
+        <v>887.59</v>
       </c>
     </row>
     <row r="945">
@@ -58080,7 +58080,7 @@
         </is>
       </c>
       <c r="M945" s="2" t="n">
-        <v>225.42</v>
+        <v>224.49</v>
       </c>
     </row>
     <row r="946">
@@ -58141,7 +58141,7 @@
         </is>
       </c>
       <c r="M946" s="2" t="n">
-        <v>3835.68</v>
+        <v>3819.88</v>
       </c>
     </row>
     <row r="947">
@@ -58202,7 +58202,7 @@
         </is>
       </c>
       <c r="M947" s="2" t="n">
-        <v>152.92</v>
+        <v>152.29</v>
       </c>
     </row>
     <row r="948">
@@ -58263,7 +58263,7 @@
         </is>
       </c>
       <c r="M948" s="2" t="n">
-        <v>17727.32</v>
+        <v>17654.26</v>
       </c>
     </row>
     <row r="949">
@@ -58324,7 +58324,7 @@
         </is>
       </c>
       <c r="M949" s="2" t="n">
-        <v>4270.69</v>
+        <v>4253.09</v>
       </c>
     </row>
     <row r="950">
@@ -58385,7 +58385,7 @@
         </is>
       </c>
       <c r="M950" s="2" t="n">
-        <v>1725.29</v>
+        <v>1718.18</v>
       </c>
     </row>
     <row r="951">
@@ -58446,7 +58446,7 @@
         </is>
       </c>
       <c r="M951" s="2" t="n">
-        <v>668.45</v>
+        <v>665.6900000000001</v>
       </c>
     </row>
     <row r="952">
@@ -58507,7 +58507,7 @@
         </is>
       </c>
       <c r="M952" s="2" t="n">
-        <v>229.56</v>
+        <v>228.61</v>
       </c>
     </row>
     <row r="953">
@@ -58568,7 +58568,7 @@
         </is>
       </c>
       <c r="M953" s="2" t="n">
-        <v>2303.59</v>
+        <v>2294.09</v>
       </c>
     </row>
     <row r="954">
@@ -58629,7 +58629,7 @@
         </is>
       </c>
       <c r="M954" s="2" t="n">
-        <v>1367.42</v>
+        <v>1361.78</v>
       </c>
     </row>
     <row r="955">
@@ -58690,7 +58690,7 @@
         </is>
       </c>
       <c r="M955" s="2" t="n">
-        <v>322.05</v>
+        <v>320.73</v>
       </c>
     </row>
     <row r="956">
@@ -58751,7 +58751,7 @@
         </is>
       </c>
       <c r="M956" s="2" t="n">
-        <v>1880.76</v>
+        <v>1873.01</v>
       </c>
     </row>
     <row r="957">
@@ -58812,7 +58812,7 @@
         </is>
       </c>
       <c r="M957" s="2" t="n">
-        <v>834.97</v>
+        <v>831.53</v>
       </c>
     </row>
     <row r="958">
@@ -58873,7 +58873,7 @@
         </is>
       </c>
       <c r="M958" s="2" t="n">
-        <v>266.28</v>
+        <v>265.19</v>
       </c>
     </row>
     <row r="959">
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="M959" s="2" t="n">
-        <v>3138.72</v>
+        <v>3125.79</v>
       </c>
     </row>
     <row r="960">
@@ -58995,7 +58995,7 @@
         </is>
       </c>
       <c r="M960" s="2" t="n">
-        <v>688.67</v>
+        <v>685.83</v>
       </c>
     </row>
     <row r="961">
@@ -59056,7 +59056,7 @@
         </is>
       </c>
       <c r="M961" s="2" t="n">
-        <v>1694.41</v>
+        <v>1687.43</v>
       </c>
     </row>
     <row r="962">
@@ -59117,7 +59117,7 @@
         </is>
       </c>
       <c r="M962" s="2" t="n">
-        <v>2136.59</v>
+        <v>2127.78</v>
       </c>
     </row>
     <row r="963">
@@ -59178,7 +59178,7 @@
         </is>
       </c>
       <c r="M963" s="2" t="n">
-        <v>19368.93</v>
+        <v>19289.1</v>
       </c>
     </row>
     <row r="964">
@@ -59239,7 +59239,7 @@
         </is>
       </c>
       <c r="M964" s="2" t="n">
-        <v>332.39</v>
+        <v>331.02</v>
       </c>
     </row>
     <row r="965">
@@ -59300,7 +59300,7 @@
         </is>
       </c>
       <c r="M965" s="2" t="n">
-        <v>294.54</v>
+        <v>293.33</v>
       </c>
     </row>
     <row r="966">
@@ -59361,7 +59361,7 @@
         </is>
       </c>
       <c r="M966" s="2" t="n">
-        <v>20523.77</v>
+        <v>20439.18</v>
       </c>
     </row>
     <row r="967">
@@ -59422,7 +59422,7 @@
         </is>
       </c>
       <c r="M967" s="2" t="n">
-        <v>988.17</v>
+        <v>984.1</v>
       </c>
     </row>
     <row r="968">
@@ -59483,7 +59483,7 @@
         </is>
       </c>
       <c r="M968" s="2" t="n">
-        <v>124.95</v>
+        <v>124.44</v>
       </c>
     </row>
     <row r="969">
@@ -59544,7 +59544,7 @@
         </is>
       </c>
       <c r="M969" s="2" t="n">
-        <v>27191.54</v>
+        <v>27079.47</v>
       </c>
     </row>
     <row r="970">
@@ -59605,7 +59605,7 @@
         </is>
       </c>
       <c r="M970" s="2" t="n">
-        <v>5269.77</v>
+        <v>5248.05</v>
       </c>
     </row>
     <row r="971">
@@ -59666,7 +59666,7 @@
         </is>
       </c>
       <c r="M971" s="2" t="n">
-        <v>4146</v>
+        <v>4128.91</v>
       </c>
     </row>
     <row r="972">
@@ -59727,7 +59727,7 @@
         </is>
       </c>
       <c r="M972" s="2" t="n">
-        <v>3713.1</v>
+        <v>3697.79</v>
       </c>
     </row>
     <row r="973">
@@ -59788,7 +59788,7 @@
         </is>
       </c>
       <c r="M973" s="2" t="n">
-        <v>2606.46</v>
+        <v>2595.72</v>
       </c>
     </row>
     <row r="974">
@@ -59849,7 +59849,7 @@
         </is>
       </c>
       <c r="M974" s="2" t="n">
-        <v>387.89</v>
+        <v>387.29</v>
       </c>
     </row>
     <row r="975">
@@ -59910,7 +59910,7 @@
         </is>
       </c>
       <c r="M975" s="2" t="n">
-        <v>534.12</v>
+        <v>533.29</v>
       </c>
     </row>
     <row r="976">
@@ -59971,7 +59971,7 @@
         </is>
       </c>
       <c r="M976" s="2" t="n">
-        <v>111.33</v>
+        <v>111.16</v>
       </c>
     </row>
     <row r="977">
@@ -60032,7 +60032,7 @@
         </is>
       </c>
       <c r="M977" s="2" t="n">
-        <v>4527.53</v>
+        <v>4520.51</v>
       </c>
     </row>
     <row r="978">
@@ -60093,7 +60093,7 @@
         </is>
       </c>
       <c r="M978" s="2" t="n">
-        <v>207.3</v>
+        <v>206.98</v>
       </c>
     </row>
     <row r="979">
@@ -60154,7 +60154,7 @@
         </is>
       </c>
       <c r="M979" s="2" t="n">
-        <v>547.88</v>
+        <v>547.03</v>
       </c>
     </row>
     <row r="980">
@@ -60215,7 +60215,7 @@
         </is>
       </c>
       <c r="M980" s="2" t="n">
-        <v>54.18</v>
+        <v>54.09</v>
       </c>
     </row>
     <row r="981">
@@ -60276,7 +60276,7 @@
         </is>
       </c>
       <c r="M981" s="2" t="n">
-        <v>81.14</v>
+        <v>81.01000000000001</v>
       </c>
     </row>
     <row r="982">
@@ -60337,7 +60337,7 @@
         </is>
       </c>
       <c r="M982" s="2" t="n">
-        <v>1144.09</v>
+        <v>1142.32</v>
       </c>
     </row>
     <row r="983">
@@ -60398,7 +60398,7 @@
         </is>
       </c>
       <c r="M983" s="2" t="n">
-        <v>427.32</v>
+        <v>426.66</v>
       </c>
     </row>
     <row r="984">
@@ -60459,7 +60459,7 @@
         </is>
       </c>
       <c r="M984" s="2" t="n">
-        <v>162.28</v>
+        <v>162.03</v>
       </c>
     </row>
     <row r="985">
@@ -60520,7 +60520,7 @@
         </is>
       </c>
       <c r="M985" s="2" t="n">
-        <v>12772.96</v>
+        <v>12753.17</v>
       </c>
     </row>
     <row r="986">
@@ -60581,7 +60581,7 @@
         </is>
       </c>
       <c r="M986" s="2" t="n">
-        <v>854.64</v>
+        <v>853.3099999999999</v>
       </c>
     </row>
     <row r="987">
@@ -60642,7 +60642,7 @@
         </is>
       </c>
       <c r="M987" s="2" t="n">
-        <v>2031.51</v>
+        <v>2028.36</v>
       </c>
     </row>
     <row r="988">
@@ -60703,7 +60703,7 @@
         </is>
       </c>
       <c r="M988" s="2" t="n">
-        <v>8549.780000000001</v>
+        <v>8536.530000000001</v>
       </c>
     </row>
     <row r="989">
@@ -60764,7 +60764,7 @@
         </is>
       </c>
       <c r="M989" s="2" t="n">
-        <v>248.76</v>
+        <v>248.37</v>
       </c>
     </row>
     <row r="990">
@@ -60825,7 +60825,7 @@
         </is>
       </c>
       <c r="M990" s="2" t="n">
-        <v>371.36</v>
+        <v>370.78</v>
       </c>
     </row>
     <row r="991">
@@ -60886,7 +60886,7 @@
         </is>
       </c>
       <c r="M991" s="2" t="n">
-        <v>319.36</v>
+        <v>318.87</v>
       </c>
     </row>
     <row r="992">
@@ -60947,7 +60947,7 @@
         </is>
       </c>
       <c r="M992" s="2" t="n">
-        <v>335.62</v>
+        <v>335.1</v>
       </c>
     </row>
     <row r="993">
@@ -61008,7 +61008,7 @@
         </is>
       </c>
       <c r="M993" s="2" t="n">
-        <v>331.68</v>
+        <v>331.17</v>
       </c>
     </row>
     <row r="994">
@@ -61069,7 +61069,7 @@
         </is>
       </c>
       <c r="M994" s="2" t="n">
-        <v>82.92</v>
+        <v>82.79000000000001</v>
       </c>
     </row>
     <row r="995">
@@ -61130,7 +61130,7 @@
         </is>
       </c>
       <c r="M995" s="2" t="n">
-        <v>78.34</v>
+        <v>78.22</v>
       </c>
     </row>
     <row r="996">
@@ -61191,7 +61191,7 @@
         </is>
       </c>
       <c r="M996" s="2" t="n">
-        <v>796.13</v>
+        <v>794.9</v>
       </c>
     </row>
     <row r="997">
@@ -61252,7 +61252,7 @@
         </is>
       </c>
       <c r="M997" s="2" t="n">
-        <v>399.85</v>
+        <v>399.23</v>
       </c>
     </row>
     <row r="998">
@@ -61313,7 +61313,7 @@
         </is>
       </c>
       <c r="M998" s="2" t="n">
-        <v>82.67</v>
+        <v>82.54000000000001</v>
       </c>
     </row>
     <row r="999">
@@ -61374,7 +61374,7 @@
         </is>
       </c>
       <c r="M999" s="2" t="n">
-        <v>215.1</v>
+        <v>214.77</v>
       </c>
     </row>
     <row r="1000">
@@ -61435,7 +61435,7 @@
         </is>
       </c>
       <c r="M1000" s="2" t="n">
-        <v>916</v>
+        <v>914.58</v>
       </c>
     </row>
     <row r="1001">
@@ -61496,7 +61496,7 @@
         </is>
       </c>
       <c r="M1001" s="2" t="n">
-        <v>737.6799999999999</v>
+        <v>736.54</v>
       </c>
     </row>
     <row r="1002">
@@ -61557,7 +61557,7 @@
         </is>
       </c>
       <c r="M1002" s="2" t="n">
-        <v>1340.4</v>
+        <v>1338.32</v>
       </c>
     </row>
     <row r="1003">
@@ -61618,7 +61618,7 @@
         </is>
       </c>
       <c r="M1003" s="2" t="n">
-        <v>14768.86</v>
+        <v>14745.97</v>
       </c>
     </row>
     <row r="1004">
@@ -61679,7 +61679,7 @@
         </is>
       </c>
       <c r="M1004" s="2" t="n">
-        <v>1595.46</v>
+        <v>1592.99</v>
       </c>
     </row>
     <row r="1005">
@@ -61740,7 +61740,7 @@
         </is>
       </c>
       <c r="M1005" s="2" t="n">
-        <v>1114.08</v>
+        <v>1112.35</v>
       </c>
     </row>
     <row r="1006">
@@ -61801,7 +61801,7 @@
         </is>
       </c>
       <c r="M1006" s="2" t="n">
-        <v>2393.67</v>
+        <v>2389.96</v>
       </c>
     </row>
     <row r="1007">
@@ -61862,7 +61862,7 @@
         </is>
       </c>
       <c r="M1007" s="2" t="n">
-        <v>687.27</v>
+        <v>686.2</v>
       </c>
     </row>
     <row r="1008">
@@ -61923,7 +61923,7 @@
         </is>
       </c>
       <c r="M1008" s="2" t="n">
-        <v>687.27</v>
+        <v>686.2</v>
       </c>
     </row>
     <row r="1009">
@@ -61984,7 +61984,7 @@
         </is>
       </c>
       <c r="M1009" s="2" t="n">
-        <v>687.27</v>
+        <v>686.2</v>
       </c>
     </row>
     <row r="1010">
@@ -62045,7 +62045,7 @@
         </is>
       </c>
       <c r="M1010" s="2" t="n">
-        <v>235.28</v>
+        <v>234.91</v>
       </c>
     </row>
     <row r="1011">
@@ -62106,7 +62106,7 @@
         </is>
       </c>
       <c r="M1011" s="2" t="n">
-        <v>1209.46</v>
+        <v>1207.59</v>
       </c>
     </row>
     <row r="1012">
@@ -62167,7 +62167,7 @@
         </is>
       </c>
       <c r="M1012" s="2" t="n">
-        <v>660.05</v>
+        <v>659.03</v>
       </c>
     </row>
     <row r="1013">
@@ -62228,7 +62228,7 @@
         </is>
       </c>
       <c r="M1013" s="2" t="n">
-        <v>1189.54</v>
+        <v>1187.7</v>
       </c>
     </row>
     <row r="1014">
@@ -62289,7 +62289,7 @@
         </is>
       </c>
       <c r="M1014" s="2" t="n">
-        <v>1137.22</v>
+        <v>1135.46</v>
       </c>
     </row>
     <row r="1015">
@@ -62350,7 +62350,7 @@
         </is>
       </c>
       <c r="M1015" s="2" t="n">
-        <v>1285.77</v>
+        <v>1283.78</v>
       </c>
     </row>
     <row r="1016">
@@ -62411,7 +62411,7 @@
         </is>
       </c>
       <c r="M1016" s="2" t="n">
-        <v>10882.07</v>
+        <v>10938.27</v>
       </c>
     </row>
     <row r="1017">
@@ -62472,7 +62472,7 @@
         </is>
       </c>
       <c r="M1017" s="2" t="n">
-        <v>121.71</v>
+        <v>122.34</v>
       </c>
     </row>
     <row r="1018">
@@ -62533,7 +62533,7 @@
         </is>
       </c>
       <c r="M1018" s="2" t="n">
-        <v>278.65</v>
+        <v>280.09</v>
       </c>
     </row>
     <row r="1019">
@@ -62594,7 +62594,7 @@
         </is>
       </c>
       <c r="M1019" s="2" t="n">
-        <v>178.49</v>
+        <v>179.42</v>
       </c>
     </row>
     <row r="1020">
@@ -62655,7 +62655,7 @@
         </is>
       </c>
       <c r="M1020" s="2" t="n">
-        <v>3404.93</v>
+        <v>3422.51</v>
       </c>
     </row>
     <row r="1021">
@@ -62716,7 +62716,7 @@
         </is>
       </c>
       <c r="M1021" s="2" t="n">
-        <v>2282.84</v>
+        <v>2294.63</v>
       </c>
     </row>
     <row r="1022">
@@ -62777,7 +62777,7 @@
         </is>
       </c>
       <c r="M1022" s="2" t="n">
-        <v>752.0599999999999</v>
+        <v>755.9400000000001</v>
       </c>
     </row>
     <row r="1023">
@@ -62838,7 +62838,7 @@
         </is>
       </c>
       <c r="M1023" s="2" t="n">
-        <v>806.64</v>
+        <v>810.8</v>
       </c>
     </row>
     <row r="1024">
@@ -62899,7 +62899,7 @@
         </is>
       </c>
       <c r="M1024" s="2" t="n">
-        <v>880.0700000000001</v>
+        <v>884.62</v>
       </c>
     </row>
     <row r="1025">
@@ -62960,7 +62960,7 @@
         </is>
       </c>
       <c r="M1025" s="2" t="n">
-        <v>1513.42</v>
+        <v>1521.23</v>
       </c>
     </row>
     <row r="1026">
@@ -63021,7 +63021,7 @@
         </is>
       </c>
       <c r="M1026" s="2" t="n">
-        <v>503.43</v>
+        <v>506.03</v>
       </c>
     </row>
     <row r="1027">
@@ -63082,7 +63082,7 @@
         </is>
       </c>
       <c r="M1027" s="2" t="n">
-        <v>331.68</v>
+        <v>333.39</v>
       </c>
     </row>
     <row r="1028">
@@ -63143,7 +63143,7 @@
         </is>
       </c>
       <c r="M1028" s="2" t="n">
-        <v>199.03</v>
+        <v>200.06</v>
       </c>
     </row>
     <row r="1029">
@@ -63204,7 +63204,7 @@
         </is>
       </c>
       <c r="M1029" s="2" t="n">
-        <v>135.44</v>
+        <v>136.14</v>
       </c>
     </row>
     <row r="1030">
@@ -63265,7 +63265,7 @@
         </is>
       </c>
       <c r="M1030" s="2" t="n">
-        <v>1194.2</v>
+        <v>1200.37</v>
       </c>
     </row>
     <row r="1031">
@@ -63326,7 +63326,7 @@
         </is>
       </c>
       <c r="M1031" s="2" t="n">
-        <v>1188.2</v>
+        <v>1194.33</v>
       </c>
     </row>
     <row r="1032">
@@ -63387,7 +63387,7 @@
         </is>
       </c>
       <c r="M1032" s="2" t="n">
-        <v>981.8099999999999</v>
+        <v>986.88</v>
       </c>
     </row>
     <row r="1033">
@@ -63448,7 +63448,7 @@
         </is>
       </c>
       <c r="M1033" s="2" t="n">
-        <v>3164.95</v>
+        <v>3181.29</v>
       </c>
     </row>
     <row r="1034">
@@ -63509,7 +63509,7 @@
         </is>
       </c>
       <c r="M1034" s="2" t="n">
-        <v>3702.76</v>
+        <v>3721.88</v>
       </c>
     </row>
     <row r="1035">
@@ -63570,7 +63570,7 @@
         </is>
       </c>
       <c r="M1035" s="2" t="n">
-        <v>138.5</v>
+        <v>139.21</v>
       </c>
     </row>
     <row r="1036">
@@ -63631,7 +63631,7 @@
         </is>
       </c>
       <c r="M1036" s="2" t="n">
-        <v>341.54</v>
+        <v>343.31</v>
       </c>
     </row>
     <row r="1037">
@@ -63692,7 +63692,7 @@
         </is>
       </c>
       <c r="M1037" s="2" t="n">
-        <v>1856.8</v>
+        <v>1866.39</v>
       </c>
     </row>
     <row r="1038">
@@ -63753,7 +63753,7 @@
         </is>
       </c>
       <c r="M1038" s="2" t="n">
-        <v>1398.17</v>
+        <v>1405.39</v>
       </c>
     </row>
     <row r="1039">
@@ -63814,7 +63814,7 @@
         </is>
       </c>
       <c r="M1039" s="2" t="n">
-        <v>449.81</v>
+        <v>452.14</v>
       </c>
     </row>
     <row r="1040">
@@ -63875,7 +63875,7 @@
         </is>
       </c>
       <c r="M1040" s="2" t="n">
-        <v>114.01</v>
+        <v>114.6</v>
       </c>
     </row>
     <row r="1041">
@@ -63936,7 +63936,7 @@
         </is>
       </c>
       <c r="M1041" s="2" t="n">
-        <v>243.42</v>
+        <v>244.68</v>
       </c>
     </row>
     <row r="1042">
@@ -63997,7 +63997,7 @@
         </is>
       </c>
       <c r="M1042" s="2" t="n">
-        <v>782.91</v>
+        <v>786.95</v>
       </c>
     </row>
     <row r="1043">
@@ -64058,7 +64058,7 @@
         </is>
       </c>
       <c r="M1043" s="2" t="n">
-        <v>3131.76</v>
+        <v>3147.93</v>
       </c>
     </row>
     <row r="1044">
@@ -64119,7 +64119,7 @@
         </is>
       </c>
       <c r="M1044" s="2" t="n">
-        <v>714.23</v>
+        <v>717.92</v>
       </c>
     </row>
     <row r="1045">
@@ -64180,7 +64180,7 @@
         </is>
       </c>
       <c r="M1045" s="2" t="n">
-        <v>514.3099999999999</v>
+        <v>516.96</v>
       </c>
     </row>
     <row r="1046">
@@ -64241,7 +64241,7 @@
         </is>
       </c>
       <c r="M1046" s="2" t="n">
-        <v>3507.06</v>
+        <v>3525.17</v>
       </c>
     </row>
     <row r="1047">
@@ -64302,7 +64302,7 @@
         </is>
       </c>
       <c r="M1047" s="2" t="n">
-        <v>1829.58</v>
+        <v>1839.03</v>
       </c>
     </row>
     <row r="1048">
@@ -64363,7 +64363,7 @@
         </is>
       </c>
       <c r="M1048" s="2" t="n">
-        <v>17333.07</v>
+        <v>17422.58</v>
       </c>
     </row>
     <row r="1049">
@@ -64424,7 +64424,7 @@
         </is>
       </c>
       <c r="M1049" s="2" t="n">
-        <v>294.57</v>
+        <v>296.09</v>
       </c>
     </row>
     <row r="1050">
@@ -64485,7 +64485,7 @@
         </is>
       </c>
       <c r="M1050" s="2" t="n">
-        <v>1024.93</v>
+        <v>1030.23</v>
       </c>
     </row>
     <row r="1051">
@@ -64546,7 +64546,7 @@
         </is>
       </c>
       <c r="M1051" s="2" t="n">
-        <v>161.26</v>
+        <v>162.09</v>
       </c>
     </row>
     <row r="1052">
@@ -64607,7 +64607,7 @@
         </is>
       </c>
       <c r="M1052" s="2" t="n">
-        <v>2454.53</v>
+        <v>2467.21</v>
       </c>
     </row>
     <row r="1053">
@@ -64668,7 +64668,7 @@
         </is>
       </c>
       <c r="M1053" s="2" t="n">
-        <v>1056.08</v>
+        <v>1061.54</v>
       </c>
     </row>
     <row r="1054">
@@ -64729,7 +64729,7 @@
         </is>
       </c>
       <c r="M1054" s="2" t="n">
-        <v>134.25</v>
+        <v>134.94</v>
       </c>
     </row>
     <row r="1055">
@@ -64790,7 +64790,7 @@
         </is>
       </c>
       <c r="M1055" s="2" t="n">
-        <v>459.11</v>
+        <v>461.48</v>
       </c>
     </row>
     <row r="1056">
@@ -64851,7 +64851,7 @@
         </is>
       </c>
       <c r="M1056" s="2" t="n">
-        <v>521.9400000000001</v>
+        <v>524.63</v>
       </c>
     </row>
     <row r="1057">
@@ -64912,7 +64912,7 @@
         </is>
       </c>
       <c r="M1057" s="2" t="n">
-        <v>557.99</v>
+        <v>560.87</v>
       </c>
     </row>
     <row r="1058">
@@ -64973,7 +64973,7 @@
         </is>
       </c>
       <c r="M1058" s="2" t="n">
-        <v>136.21</v>
+        <v>136.91</v>
       </c>
     </row>
     <row r="1059">
@@ -65034,7 +65034,7 @@
         </is>
       </c>
       <c r="M1059" s="2" t="n">
-        <v>479.46</v>
+        <v>481.94</v>
       </c>
     </row>
     <row r="1060">
@@ -65095,7 +65095,7 @@
         </is>
       </c>
       <c r="M1060" s="2" t="n">
-        <v>129.45</v>
+        <v>130.12</v>
       </c>
     </row>
     <row r="1061">
@@ -65156,7 +65156,7 @@
         </is>
       </c>
       <c r="M1061" s="2" t="n">
-        <v>724.66</v>
+        <v>728.4</v>
       </c>
     </row>
     <row r="1062">
@@ -65217,7 +65217,7 @@
         </is>
       </c>
       <c r="M1062" s="2" t="n">
-        <v>759.3200000000001</v>
+        <v>763.24</v>
       </c>
     </row>
     <row r="1063">
@@ -65278,7 +65278,7 @@
         </is>
       </c>
       <c r="M1063" s="2" t="n">
-        <v>228.92</v>
+        <v>230.1</v>
       </c>
     </row>
     <row r="1064">
@@ -65339,7 +65339,7 @@
         </is>
       </c>
       <c r="M1064" s="2" t="n">
-        <v>208.14</v>
+        <v>209.21</v>
       </c>
     </row>
     <row r="1065">
@@ -65400,7 +65400,7 @@
         </is>
       </c>
       <c r="M1065" s="2" t="n">
-        <v>497.52</v>
+        <v>500.09</v>
       </c>
     </row>
     <row r="1066">
@@ -65461,7 +65461,7 @@
         </is>
       </c>
       <c r="M1066" s="2" t="n">
-        <v>542.66</v>
+        <v>545.46</v>
       </c>
     </row>
     <row r="1067">
@@ -65522,7 +65522,7 @@
         </is>
       </c>
       <c r="M1067" s="2" t="n">
-        <v>1299.76</v>
+        <v>1306.47</v>
       </c>
     </row>
     <row r="1068">
@@ -65583,7 +65583,7 @@
         </is>
       </c>
       <c r="M1068" s="2" t="n">
-        <v>28029.5</v>
+        <v>28174.26</v>
       </c>
     </row>
     <row r="1069">
@@ -65644,7 +65644,7 @@
         </is>
       </c>
       <c r="M1069" s="2" t="n">
-        <v>158.46</v>
+        <v>159.28</v>
       </c>
     </row>
     <row r="1070">
@@ -65705,7 +65705,7 @@
         </is>
       </c>
       <c r="M1070" s="2" t="n">
-        <v>5356.73</v>
+        <v>5394.54</v>
       </c>
     </row>
     <row r="1071">
@@ -65766,7 +65766,7 @@
         </is>
       </c>
       <c r="M1071" s="2" t="n">
-        <v>1651.79</v>
+        <v>1663.44</v>
       </c>
     </row>
     <row r="1072">
@@ -65827,7 +65827,7 @@
         </is>
       </c>
       <c r="M1072" s="2" t="n">
-        <v>1651.79</v>
+        <v>1663.44</v>
       </c>
     </row>
     <row r="1073">
@@ -65888,7 +65888,7 @@
         </is>
       </c>
       <c r="M1073" s="2" t="n">
-        <v>618.08</v>
+        <v>622.45</v>
       </c>
     </row>
     <row r="1074">
@@ -65949,7 +65949,7 @@
         </is>
       </c>
       <c r="M1074" s="2" t="n">
-        <v>628.77</v>
+        <v>633.2</v>
       </c>
     </row>
     <row r="1075">
@@ -66010,7 +66010,7 @@
         </is>
       </c>
       <c r="M1075" s="2" t="n">
-        <v>4302.63</v>
+        <v>4333</v>
       </c>
     </row>
     <row r="1076">
@@ -66071,7 +66071,7 @@
         </is>
       </c>
       <c r="M1076" s="2" t="n">
-        <v>550.9299999999999</v>
+        <v>554.8200000000001</v>
       </c>
     </row>
     <row r="1077">
@@ -66132,7 +66132,7 @@
         </is>
       </c>
       <c r="M1077" s="2" t="n">
-        <v>11898.07</v>
+        <v>11982.05</v>
       </c>
     </row>
     <row r="1078">
@@ -66193,7 +66193,7 @@
         </is>
       </c>
       <c r="M1078" s="2" t="n">
-        <v>433.68</v>
+        <v>436.74</v>
       </c>
     </row>
     <row r="1079">
@@ -66254,7 +66254,7 @@
         </is>
       </c>
       <c r="M1079" s="2" t="n">
-        <v>1323.92</v>
+        <v>1333.27</v>
       </c>
     </row>
     <row r="1080">
@@ -66315,7 +66315,7 @@
         </is>
       </c>
       <c r="M1080" s="2" t="n">
-        <v>375.03</v>
+        <v>377.68</v>
       </c>
     </row>
     <row r="1081">
@@ -66376,7 +66376,7 @@
         </is>
       </c>
       <c r="M1081" s="2" t="n">
-        <v>1841.54</v>
+        <v>1854.53</v>
       </c>
     </row>
     <row r="1082">
@@ -66437,7 +66437,7 @@
         </is>
       </c>
       <c r="M1082" s="2" t="n">
-        <v>916.26</v>
+        <v>922.72</v>
       </c>
     </row>
     <row r="1083">
@@ -66498,7 +66498,7 @@
         </is>
       </c>
       <c r="M1083" s="2" t="n">
-        <v>331.72</v>
+        <v>334.06</v>
       </c>
     </row>
     <row r="1084">
@@ -66559,7 +66559,7 @@
         </is>
       </c>
       <c r="M1084" s="2" t="n">
-        <v>36932.45</v>
+        <v>37193.1</v>
       </c>
     </row>
     <row r="1085">
@@ -66620,7 +66620,7 @@
         </is>
       </c>
       <c r="M1085" s="2" t="n">
-        <v>186.19</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="1086">
@@ -66681,7 +66681,7 @@
         </is>
       </c>
       <c r="M1086" s="2" t="n">
-        <v>547.25</v>
+        <v>551.11</v>
       </c>
     </row>
     <row r="1087">
@@ -66742,7 +66742,7 @@
         </is>
       </c>
       <c r="M1087" s="2" t="n">
-        <v>371.36</v>
+        <v>373.98</v>
       </c>
     </row>
     <row r="1088">
@@ -66803,7 +66803,7 @@
         </is>
       </c>
       <c r="M1088" s="2" t="n">
-        <v>1110.55</v>
+        <v>1118.39</v>
       </c>
     </row>
     <row r="1089">
@@ -66864,7 +66864,7 @@
         </is>
       </c>
       <c r="M1089" s="2" t="n">
-        <v>273.92</v>
+        <v>275.85</v>
       </c>
     </row>
     <row r="1090">
@@ -66925,7 +66925,7 @@
         </is>
       </c>
       <c r="M1090" s="2" t="n">
-        <v>7226.02</v>
+        <v>7277.02</v>
       </c>
     </row>
     <row r="1091">
@@ -66986,7 +66986,7 @@
         </is>
       </c>
       <c r="M1091" s="2" t="n">
-        <v>8274.08</v>
+        <v>8332.48</v>
       </c>
     </row>
     <row r="1092">
@@ -67047,7 +67047,7 @@
         </is>
       </c>
       <c r="M1092" s="2" t="n">
-        <v>1370.29</v>
+        <v>1379.96</v>
       </c>
     </row>
     <row r="1093">
@@ -67108,7 +67108,7 @@
         </is>
       </c>
       <c r="M1093" s="2" t="n">
-        <v>15320.67</v>
+        <v>15428.8</v>
       </c>
     </row>
     <row r="1094">
@@ -67169,7 +67169,7 @@
         </is>
       </c>
       <c r="M1094" s="2" t="n">
-        <v>478.44</v>
+        <v>481.82</v>
       </c>
     </row>
     <row r="1095">
@@ -67230,7 +67230,7 @@
         </is>
       </c>
       <c r="M1095" s="2" t="n">
-        <v>1579.55</v>
+        <v>1590.7</v>
       </c>
     </row>
     <row r="1096">
@@ -67291,7 +67291,7 @@
         </is>
       </c>
       <c r="M1096" s="2" t="n">
-        <v>854.67</v>
+        <v>860.71</v>
       </c>
     </row>
     <row r="1097">
@@ -67352,7 +67352,7 @@
         </is>
       </c>
       <c r="M1097" s="2" t="n">
-        <v>1559.28</v>
+        <v>1570.28</v>
       </c>
     </row>
     <row r="1098">
@@ -67413,7 +67413,7 @@
         </is>
       </c>
       <c r="M1098" s="2" t="n">
-        <v>1032.99</v>
+        <v>1040.28</v>
       </c>
     </row>
     <row r="1099">
@@ -67474,7 +67474,7 @@
         </is>
       </c>
       <c r="M1099" s="2" t="n">
-        <v>3588.96</v>
+        <v>3614.29</v>
       </c>
     </row>
     <row r="1100">
@@ -67535,7 +67535,7 @@
         </is>
       </c>
       <c r="M1100" s="2" t="n">
-        <v>373.14</v>
+        <v>375.77</v>
       </c>
     </row>
     <row r="1101">
@@ -67596,7 +67596,7 @@
         </is>
       </c>
       <c r="M1101" s="2" t="n">
-        <v>69.59</v>
+        <v>70.08</v>
       </c>
     </row>
     <row r="1102">
@@ -67657,7 +67657,7 @@
         </is>
       </c>
       <c r="M1102" s="2" t="n">
-        <v>111.28</v>
+        <v>112.07</v>
       </c>
     </row>
     <row r="1103">
@@ -67718,7 +67718,7 @@
         </is>
       </c>
       <c r="M1103" s="2" t="n">
-        <v>356.1</v>
+        <v>358.61</v>
       </c>
     </row>
     <row r="1104">
@@ -67779,7 +67779,7 @@
         </is>
       </c>
       <c r="M1104" s="2" t="n">
-        <v>806.64</v>
+        <v>812.33</v>
       </c>
     </row>
     <row r="1105">
@@ -67840,7 +67840,7 @@
         </is>
       </c>
       <c r="M1105" s="2" t="n">
-        <v>742.72</v>
+        <v>747.96</v>
       </c>
     </row>
     <row r="1106">
@@ -67901,7 +67901,7 @@
         </is>
       </c>
       <c r="M1106" s="2" t="n">
-        <v>322.47</v>
+        <v>324.75</v>
       </c>
     </row>
     <row r="1107">
@@ -67962,7 +67962,7 @@
         </is>
       </c>
       <c r="M1107" s="2" t="n">
-        <v>80.89</v>
+        <v>81.45999999999999</v>
       </c>
     </row>
     <row r="1108">
@@ -68023,7 +68023,7 @@
         </is>
       </c>
       <c r="M1108" s="2" t="n">
-        <v>210.48</v>
+        <v>211.96</v>
       </c>
     </row>
     <row r="1109">
@@ -68084,7 +68084,7 @@
         </is>
       </c>
       <c r="M1109" s="2" t="n">
-        <v>7536.64</v>
+        <v>7589.83</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/gas-licuado-de-petroleo/nov-2025.xlsx
+++ b/docs/oc-mensuales/gas-licuado-de-petroleo/nov-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC nov-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC nov-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -19760,7 +19760,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19821,7 +19821,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -20309,7 +20309,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21773,7 +21773,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -21834,7 +21834,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -22810,7 +22810,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -22871,7 +22871,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -23542,7 +23542,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -23786,7 +23786,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -23847,7 +23847,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -24213,7 +24213,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -24274,7 +24274,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25799,7 +25799,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -26104,7 +26104,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -26287,7 +26287,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -26470,7 +26470,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -26653,7 +26653,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -27141,7 +27141,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -27324,7 +27324,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -28178,7 +28178,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28422,7 +28422,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -29215,7 +29215,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -29825,7 +29825,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -30069,7 +30069,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -30252,7 +30252,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -30374,7 +30374,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -30984,7 +30984,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -32204,7 +32204,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -32814,7 +32814,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -32875,7 +32875,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -33119,7 +33119,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -33546,7 +33546,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -34156,7 +34156,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -34400,7 +34400,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -34644,7 +34644,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -34888,7 +34888,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -35010,7 +35010,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35193,7 +35193,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -35498,7 +35498,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -35681,7 +35681,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -36108,7 +36108,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -36474,7 +36474,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -36535,7 +36535,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -36962,7 +36962,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -37084,7 +37084,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -37206,7 +37206,7 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
@@ -37267,7 +37267,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -37389,7 +37389,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -37934,7 +37934,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -38178,7 +38178,7 @@
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
@@ -38239,7 +38239,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -38727,7 +38727,7 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -38788,7 +38788,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -40557,7 +40557,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -40618,7 +40618,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -40801,7 +40801,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -41472,7 +41472,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -41655,7 +41655,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -41777,7 +41777,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -41899,7 +41899,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -41960,7 +41960,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -42021,7 +42021,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -42143,7 +42143,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -42326,7 +42326,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -42387,7 +42387,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -42448,7 +42448,7 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -42509,7 +42509,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -43607,7 +43607,7 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -44400,7 +44400,7 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
@@ -44583,7 +44583,7 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
@@ -45132,7 +45132,7 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
@@ -45498,7 +45498,7 @@
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
@@ -45681,7 +45681,7 @@
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
@@ -45742,7 +45742,7 @@
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
@@ -45925,7 +45925,7 @@
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
@@ -46535,7 +46535,7 @@
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I756" t="inlineStr">
@@ -46718,7 +46718,7 @@
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
@@ -46840,7 +46840,7 @@
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
@@ -47023,7 +47023,7 @@
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I764" t="inlineStr">
@@ -47084,7 +47084,7 @@
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
@@ -48243,7 +48243,7 @@
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I784" t="inlineStr">
@@ -48365,7 +48365,7 @@
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I786" t="inlineStr">
@@ -48792,7 +48792,7 @@
       </c>
       <c r="H793" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I793" t="inlineStr">
@@ -49036,7 +49036,7 @@
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I797" t="inlineStr">
@@ -49097,7 +49097,7 @@
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I798" t="inlineStr">
@@ -49219,7 +49219,7 @@
       </c>
       <c r="H800" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I800" t="inlineStr">
@@ -49341,7 +49341,7 @@
       </c>
       <c r="H802" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I802" t="inlineStr">
@@ -50801,7 +50801,7 @@
       </c>
       <c r="H826" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I826" t="inlineStr">
@@ -50984,7 +50984,7 @@
       </c>
       <c r="H829" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I829" t="inlineStr">
@@ -51411,7 +51411,7 @@
       </c>
       <c r="H836" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I836" t="inlineStr">
@@ -51655,7 +51655,7 @@
       </c>
       <c r="H840" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I840" t="inlineStr">
@@ -52143,7 +52143,7 @@
       </c>
       <c r="H848" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I848" t="inlineStr">
@@ -52692,7 +52692,7 @@
       </c>
       <c r="H857" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I857" t="inlineStr">
@@ -52936,7 +52936,7 @@
       </c>
       <c r="H861" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I861" t="inlineStr">
@@ -53363,7 +53363,7 @@
       </c>
       <c r="H868" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I868" t="inlineStr">
@@ -53485,7 +53485,7 @@
       </c>
       <c r="H870" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I870" t="inlineStr">
@@ -54278,7 +54278,7 @@
       </c>
       <c r="H883" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I883" t="inlineStr">
@@ -54461,7 +54461,7 @@
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I886" t="inlineStr">
@@ -54644,7 +54644,7 @@
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I889" t="inlineStr">
@@ -55010,7 +55010,7 @@
       </c>
       <c r="H895" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I895" t="inlineStr">
@@ -55193,7 +55193,7 @@
       </c>
       <c r="H898" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I898" t="inlineStr">
@@ -55376,7 +55376,7 @@
       </c>
       <c r="H901" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I901" t="inlineStr">
@@ -57023,7 +57023,7 @@
       </c>
       <c r="H928" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I928" t="inlineStr">
@@ -57389,7 +57389,7 @@
       </c>
       <c r="H934" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I934" t="inlineStr">
@@ -57450,7 +57450,7 @@
       </c>
       <c r="H935" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I935" t="inlineStr">
@@ -57694,7 +57694,7 @@
       </c>
       <c r="H939" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I939" t="inlineStr">
@@ -58548,7 +58548,7 @@
       </c>
       <c r="H953" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I953" t="inlineStr">
@@ -59219,7 +59219,7 @@
       </c>
       <c r="H964" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I964" t="inlineStr">
@@ -60073,7 +60073,7 @@
       </c>
       <c r="H978" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I978" t="inlineStr">
@@ -60195,7 +60195,7 @@
       </c>
       <c r="H980" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I980" t="inlineStr">
@@ -60256,7 +60256,7 @@
       </c>
       <c r="H981" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I981" t="inlineStr">
@@ -60439,7 +60439,7 @@
       </c>
       <c r="H984" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I984" t="inlineStr">
@@ -60500,7 +60500,7 @@
       </c>
       <c r="H985" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I985" t="inlineStr">
@@ -60744,7 +60744,7 @@
       </c>
       <c r="H989" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I989" t="inlineStr">
@@ -61049,7 +61049,7 @@
       </c>
       <c r="H994" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I994" t="inlineStr">
@@ -61293,7 +61293,7 @@
       </c>
       <c r="H998" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I998" t="inlineStr">
@@ -61354,7 +61354,7 @@
       </c>
       <c r="H999" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I999" t="inlineStr">
@@ -61415,7 +61415,7 @@
       </c>
       <c r="H1000" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1000" t="inlineStr">
@@ -61659,7 +61659,7 @@
       </c>
       <c r="H1004" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1004" t="inlineStr">
@@ -61842,7 +61842,7 @@
       </c>
       <c r="H1007" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1007" t="inlineStr">
@@ -61903,7 +61903,7 @@
       </c>
       <c r="H1008" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1008" t="inlineStr">
@@ -61964,7 +61964,7 @@
       </c>
       <c r="H1009" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1009" t="inlineStr">
@@ -62391,7 +62391,7 @@
       </c>
       <c r="H1016" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1016" t="inlineStr">
@@ -62452,7 +62452,7 @@
       </c>
       <c r="H1017" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1017" t="inlineStr">
@@ -62818,7 +62818,7 @@
       </c>
       <c r="H1023" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1023" t="inlineStr">
@@ -62940,7 +62940,7 @@
       </c>
       <c r="H1025" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1025" t="inlineStr">
@@ -63062,7 +63062,7 @@
       </c>
       <c r="H1027" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1027" t="inlineStr">
@@ -63184,7 +63184,7 @@
       </c>
       <c r="H1029" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1029" t="inlineStr">
@@ -63428,7 +63428,7 @@
       </c>
       <c r="H1033" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1033" t="inlineStr">
@@ -63550,7 +63550,7 @@
       </c>
       <c r="H1035" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1035" t="inlineStr">
@@ -63916,7 +63916,7 @@
       </c>
       <c r="H1041" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1041" t="inlineStr">
@@ -64526,7 +64526,7 @@
       </c>
       <c r="H1051" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1051" t="inlineStr">
@@ -65380,7 +65380,7 @@
       </c>
       <c r="H1065" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1065" t="inlineStr">
@@ -65441,7 +65441,7 @@
       </c>
       <c r="H1066" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1066" t="inlineStr">
@@ -65868,7 +65868,7 @@
       </c>
       <c r="H1073" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1073" t="inlineStr">
@@ -66112,7 +66112,7 @@
       </c>
       <c r="H1077" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1077" t="inlineStr">
@@ -66478,7 +66478,7 @@
       </c>
       <c r="H1083" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1083" t="inlineStr">
@@ -67454,7 +67454,7 @@
       </c>
       <c r="H1099" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1099" t="inlineStr">

--- a/docs/oc-mensuales/gas-licuado-de-petroleo/nov-2025.xlsx
+++ b/docs/oc-mensuales/gas-licuado-de-petroleo/nov-2025.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Contulmo - Educación</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Colina 1</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tribunal de Juicio Oral en lo Pena de Talca</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION XI REGION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>CORPORACIÓN SOCIAL Y CULTURAL DE CONCEPCIÓN - SEMC</t>
+          <t>CORPORACION SOCIAL Y CULTURA DE CONCEPCION - SEMCO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Protección</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO BIENESTAR SOCIAL IIA ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO BIENESTAR SOCIAL IIA ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA PRIMERA ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Servicio de Educación Pública Santa Corina</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví- Educación</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Los Alamos - Dpto Salud</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Servicio de Educación Pública Santa Corina</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile CET Antofagasta II Región</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Los Alamos - Dpto Salud</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Los Alamos - Dpto Salud</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Los Alamos - Dpto Salud</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Los Alamos - Dpto Salud</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Los Alamos - Dpto Salud</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Los Alamos - Dpto Salud</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Santa Barbara - Salud</t>
+          <t>I MUNICIPALIDAD DE SANTA BARBARA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>ESCUELA DE FORMACIÓN DE CARABINEROS LOS ANDES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIa. ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLÁS D. EDUCACIÓN</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dirección de Administración de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Centro Telecomunicaciones Navales de Antofagasta</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>BASE INFANTERIA DE MARINA TUMBES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>CORPORACION SOCIAL Y CULTURAL DE CONCEPCION- SEMCO</t>
+          <t>CORPORACION SOCIAL Y CULTURA DE CONCEPCION - SEMCO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA METROPOLITANA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NIQUEN</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE COQUIMBO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE SAN ANTONIO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hospital de Ancud</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Zona de Bienestar "Coyhaique"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>IMunicipalidad de San Pablo - Educación</t>
+          <t>I MUNICIPALIDAD DE SAN PABLO</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUELLON</t>
+          <t>Ilustre Municipalidad De Quellón</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - X Zona Los Lagos</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11463,12 +11463,12 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PUBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>BASE DE SUBMARINOS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Región Metropolitana</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>ESTACION NAVAL METROPOLITANA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIENESTAR SALUD MUNICIPAL</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Región Metropolitana</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13232,7 +13232,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13659,7 +13659,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13903,7 +13903,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CASTRO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14086,7 +14086,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo CDP Curacautín</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14696,7 +14696,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -14879,7 +14879,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SAMU</t>
+          <t>Centro Metropolitano de Atención Prehospitalaria</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15001,7 +15001,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15184,7 +15184,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>DELEGACION PRESIDENCIAL PROVINCIAL DE OSORNO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE OSORNO</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>BASE NAVAL PUERTO MONTT</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Juzgado de Letras del Trabajo de Castro</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15733,7 +15733,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>DELEGACION PRESIDENCIAL PROVINCIAL DE LOS ANDES</t>
+          <t>GOBERNACION PROVINCIAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15916,7 +15916,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16099,7 +16099,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16526,7 +16526,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Menores</t>
+          <t>SERVICIO NACIONAL DE MENORES</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -16953,7 +16953,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del CCP Linares</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -17014,7 +17014,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17622,7 +17622,11 @@
           <t>61.980.840-1</t>
         </is>
       </c>
-      <c r="G282" t="inlineStr"/>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
       <c r="H282" t="inlineStr">
         <is>
           <t>Aysén</t>
@@ -17681,7 +17685,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -17742,7 +17746,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -17925,7 +17929,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -18047,7 +18051,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Colina 1</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18108,7 +18112,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE PUERTO MONTT</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18169,7 +18173,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18230,7 +18234,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -18291,7 +18295,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18352,7 +18356,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -18413,7 +18417,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18474,7 +18478,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -18535,12 +18539,12 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18596,7 +18600,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -18718,7 +18722,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -18779,12 +18783,12 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>IIª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18840,12 +18844,12 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>IIª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18901,7 +18905,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -19450,7 +19454,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -19572,7 +19576,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -19877,7 +19881,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -20060,7 +20064,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -20121,7 +20125,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -20304,7 +20308,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LITUECHE</t>
+          <t>Hospital de Litueche</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -20426,12 +20430,12 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>DIRECCION DE INTELIGENCIA DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20609,7 +20613,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -20670,7 +20674,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -20914,7 +20918,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -21148,7 +21152,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -21158,7 +21162,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CALDERA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -21219,7 +21223,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -21402,7 +21406,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -21463,7 +21467,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -21585,7 +21589,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -21646,7 +21650,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -21707,7 +21711,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -21951,7 +21955,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -22134,7 +22138,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -22256,7 +22260,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -22683,7 +22687,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -22805,7 +22809,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL F</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -22988,7 +22992,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -23171,7 +23175,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICAC</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -23354,7 +23358,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -23415,7 +23419,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -23720,7 +23724,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -23781,7 +23785,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONTULMO</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -24391,7 +24395,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Menores</t>
+          <t>SERVICIO NACIONAL DE MENORES</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -24452,7 +24456,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -24513,7 +24517,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -24635,7 +24639,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -24696,7 +24700,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -25184,7 +25188,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>JEFATURA DE BIENESTAR (I.P)</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -25306,7 +25310,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -25367,7 +25371,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -25489,7 +25493,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -25611,7 +25615,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -25672,7 +25676,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -26099,7 +26103,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -26160,7 +26164,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -26404,7 +26408,7 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -26648,7 +26652,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -27136,7 +27140,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -27258,7 +27262,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -27624,7 +27628,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIENESTAR DEL PERSONAL CMPA</t>
+          <t>I MUNICIPALIDAD DE PUENTE ALTO</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -27807,7 +27811,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -27929,7 +27933,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -28173,7 +28177,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>BASE INFANTERIA DE MARINA TUMBES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -28234,7 +28238,7 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -28478,7 +28482,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA METROPOLITANA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -28539,7 +28543,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
@@ -28783,7 +28787,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO BIENESTAR SOCIAL IIA ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
@@ -28905,7 +28909,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
@@ -29337,7 +29341,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -29454,7 +29458,7 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>DIRECCION DE INVESTIGACION, DESARROLLO DE LA ARMA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -29515,7 +29519,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -29698,7 +29702,7 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Río Negro - Salud</t>
+          <t>I MUNICIPALIDAD DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -29759,7 +29763,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -29820,7 +29824,7 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -29881,7 +29885,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>Academia de Guerra Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
@@ -29942,7 +29946,7 @@
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>Ejército de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
@@ -30003,7 +30007,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>Ejército de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
@@ -30064,7 +30068,7 @@
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -30308,7 +30312,7 @@
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
@@ -30369,7 +30373,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Concepción" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -30491,7 +30495,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
@@ -30557,7 +30561,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -30674,7 +30678,7 @@
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
@@ -30857,7 +30861,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
@@ -31101,7 +31105,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Valdivia</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
@@ -31223,7 +31227,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
@@ -31528,7 +31532,7 @@
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -31833,7 +31837,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>ESCUELA NAVAL "ARTURO PRAT"</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
@@ -31955,7 +31959,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
@@ -32016,7 +32020,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICAC</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H518" t="inlineStr">
@@ -32077,7 +32081,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo de Osorno</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
@@ -32138,7 +32142,7 @@
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
@@ -32321,7 +32325,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del CDP Talagante</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -32494,7 +32498,7 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
@@ -32504,7 +32508,7 @@
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>Contraloría de la Armada</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H526" t="inlineStr">
@@ -32626,7 +32630,7 @@
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo de Osorno</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -33175,7 +33179,7 @@
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H537" t="inlineStr">
@@ -33480,7 +33484,7 @@
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
@@ -33602,7 +33606,7 @@
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
@@ -33663,7 +33667,7 @@
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
@@ -33785,7 +33789,7 @@
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -33846,7 +33850,7 @@
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
@@ -33907,7 +33911,7 @@
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
@@ -34029,7 +34033,7 @@
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
@@ -34212,7 +34216,7 @@
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H554" t="inlineStr">
@@ -34273,7 +34277,7 @@
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>CORP MUNIC DE QUELLON PARA LA EDUC SALUD</t>
+          <t>Corporación Municipal de Quellón</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
@@ -34334,7 +34338,7 @@
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -34517,7 +34521,7 @@
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Colina 1</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
@@ -34751,7 +34755,7 @@
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F563" t="inlineStr">
@@ -34761,7 +34765,7 @@
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CALDERA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
@@ -34822,12 +34826,12 @@
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -34944,7 +34948,7 @@
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H566" t="inlineStr">
@@ -35005,7 +35009,7 @@
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
@@ -35066,7 +35070,7 @@
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
@@ -35249,7 +35253,7 @@
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H571" t="inlineStr">
@@ -35432,12 +35436,12 @@
       </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -35554,7 +35558,7 @@
       </c>
       <c r="G576" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUELLON</t>
+          <t>Ilustre Municipalidad De Quellón</t>
         </is>
       </c>
       <c r="H576" t="inlineStr">
@@ -35615,7 +35619,7 @@
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H577" t="inlineStr">
@@ -35859,7 +35863,7 @@
       </c>
       <c r="G581" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del CCP Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H581" t="inlineStr">
@@ -36093,7 +36097,7 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F585" t="inlineStr">
@@ -36103,7 +36107,7 @@
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIa. ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
@@ -36164,7 +36168,7 @@
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
@@ -36286,7 +36290,7 @@
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H588" t="inlineStr">
@@ -36347,7 +36351,7 @@
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>Hospital de Queilen</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H589" t="inlineStr">
@@ -36591,7 +36595,7 @@
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>JEFATURA DE BIENESTAR (I.P)</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
@@ -37018,12 +37022,12 @@
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -37323,7 +37327,7 @@
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H605" t="inlineStr">
@@ -37384,7 +37388,7 @@
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H606" t="inlineStr">
@@ -37445,7 +37449,7 @@
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
@@ -37504,7 +37508,11 @@
           <t>61.980.840-1</t>
         </is>
       </c>
-      <c r="G608" t="inlineStr"/>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
       <c r="H608" t="inlineStr">
         <is>
           <t>Aysén</t>
@@ -37624,7 +37632,7 @@
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H610" t="inlineStr">
@@ -37746,7 +37754,7 @@
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMA</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
         </is>
       </c>
       <c r="H612" t="inlineStr">
@@ -37868,7 +37876,7 @@
       </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H614" t="inlineStr">
@@ -37929,7 +37937,7 @@
       </c>
       <c r="G615" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE TALCAHUANO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H615" t="inlineStr">
@@ -37990,7 +37998,7 @@
       </c>
       <c r="G616" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H616" t="inlineStr">
@@ -38112,7 +38120,7 @@
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H618" t="inlineStr">
@@ -38356,7 +38364,7 @@
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CASTRO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
@@ -38478,7 +38486,7 @@
       </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H624" t="inlineStr">
@@ -38600,7 +38608,7 @@
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H626" t="inlineStr">
@@ -38661,7 +38669,7 @@
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmeria</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H627" t="inlineStr">
@@ -38844,7 +38852,7 @@
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H630" t="inlineStr">
@@ -38905,7 +38913,7 @@
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H631" t="inlineStr">
@@ -39088,7 +39096,7 @@
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
@@ -39149,7 +39157,7 @@
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>Tribunal de Juicio Oral en lo Pena de Talca</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
@@ -39210,7 +39218,7 @@
       </c>
       <c r="G636" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H636" t="inlineStr">
@@ -39332,7 +39340,7 @@
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H638" t="inlineStr">
@@ -39576,7 +39584,7 @@
       </c>
       <c r="G642" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H642" t="inlineStr">
@@ -39759,7 +39767,7 @@
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H645" t="inlineStr">
@@ -39820,7 +39828,7 @@
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo CDP Villarrica</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H646" t="inlineStr">
@@ -40369,7 +40377,7 @@
       </c>
       <c r="G655" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H655" t="inlineStr">
@@ -40491,7 +40499,7 @@
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
@@ -40557,7 +40565,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -40618,7 +40626,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -40674,7 +40682,7 @@
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H660" t="inlineStr">
@@ -40801,7 +40809,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -40857,7 +40865,7 @@
       </c>
       <c r="G663" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H663" t="inlineStr">
@@ -40918,7 +40926,7 @@
       </c>
       <c r="G664" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H664" t="inlineStr">
@@ -41101,7 +41109,7 @@
       </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H667" t="inlineStr">
@@ -41284,7 +41292,7 @@
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H670" t="inlineStr">
@@ -41345,7 +41353,7 @@
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
@@ -41472,7 +41480,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -41528,7 +41536,7 @@
       </c>
       <c r="G674" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H674" t="inlineStr">
@@ -41589,7 +41597,7 @@
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H675" t="inlineStr">
@@ -41655,7 +41663,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -41711,7 +41719,7 @@
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>Servicio Agricola y Ganadero</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H677" t="inlineStr">
@@ -41777,7 +41785,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -41833,7 +41841,7 @@
       </c>
       <c r="G679" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H679" t="inlineStr">
@@ -41899,7 +41907,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -41960,7 +41968,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -42021,7 +42029,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -42204,7 +42212,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -42260,7 +42268,7 @@
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H686" t="inlineStr">
@@ -42326,7 +42334,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -42387,7 +42395,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -42448,7 +42456,7 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -42687,7 +42695,7 @@
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>DIRECCION DE EDUCACION</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
@@ -42992,7 +43000,7 @@
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H698" t="inlineStr">
@@ -43419,12 +43427,12 @@
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>Direccion Admin. Salud Municipal Florida</t>
+          <t>I MUNICIPALIDAD DE FLORIDA</t>
         </is>
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -43480,12 +43488,12 @@
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>Direccion Admin. Salud Municipal Florida</t>
+          <t>I MUNICIPALIDAD DE FLORIDA</t>
         </is>
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
@@ -43602,7 +43610,7 @@
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H708" t="inlineStr">
@@ -44029,7 +44037,7 @@
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>JEFATURA DE BIENESTAR (I.P)</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
@@ -44090,12 +44098,12 @@
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>Direccion Admin. Salud Municipal Florida</t>
+          <t>I MUNICIPALIDAD DE FLORIDA</t>
         </is>
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
@@ -44151,12 +44159,12 @@
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>Direccion Admin. Salud Municipal Florida</t>
+          <t>I MUNICIPALIDAD DE FLORIDA</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
@@ -44212,12 +44220,12 @@
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>Direccion Admin. Salud Municipal Florida</t>
+          <t>I MUNICIPALIDAD DE FLORIDA</t>
         </is>
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
@@ -44456,7 +44464,7 @@
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
@@ -44578,7 +44586,7 @@
       </c>
       <c r="G724" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO BIENESTAR SOCIAL IIA ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H724" t="inlineStr">
@@ -44700,7 +44708,7 @@
       </c>
       <c r="G726" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H726" t="inlineStr">
@@ -44761,7 +44769,7 @@
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo de Gendarmería</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
@@ -44822,7 +44830,7 @@
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H728" t="inlineStr">
@@ -45005,7 +45013,7 @@
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H731" t="inlineStr">
@@ -45066,7 +45074,7 @@
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
@@ -45310,7 +45318,7 @@
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
@@ -45493,7 +45501,7 @@
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H739" t="inlineStr">
@@ -45554,7 +45562,7 @@
       </c>
       <c r="G740" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H740" t="inlineStr">
@@ -45615,7 +45623,7 @@
       </c>
       <c r="G741" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H741" t="inlineStr">
@@ -45676,7 +45684,7 @@
       </c>
       <c r="G742" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H742" t="inlineStr">
@@ -45737,7 +45745,7 @@
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
@@ -45798,7 +45806,7 @@
       </c>
       <c r="G744" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H744" t="inlineStr">
@@ -45859,7 +45867,7 @@
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H745" t="inlineStr">
@@ -45981,7 +45989,7 @@
       </c>
       <c r="G747" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H747" t="inlineStr">
@@ -46042,7 +46050,7 @@
       </c>
       <c r="G748" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo de Osorno</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H748" t="inlineStr">
@@ -46103,7 +46111,7 @@
       </c>
       <c r="G749" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H749" t="inlineStr">
@@ -46408,7 +46416,7 @@
       </c>
       <c r="G754" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H754" t="inlineStr">
@@ -46469,7 +46477,7 @@
       </c>
       <c r="G755" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H755" t="inlineStr">
@@ -46591,7 +46599,7 @@
       </c>
       <c r="G757" t="inlineStr">
         <is>
-          <t>JUZGADO DE LETRA Y GARANTIA DE LA UNION</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H757" t="inlineStr">
@@ -46713,7 +46721,7 @@
       </c>
       <c r="G759" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Antuco - Educación</t>
+          <t>I MUNICIPALIDAD DE ANTUCO</t>
         </is>
       </c>
       <c r="H759" t="inlineStr">
@@ -46835,7 +46843,7 @@
       </c>
       <c r="G761" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H761" t="inlineStr">
@@ -46896,7 +46904,7 @@
       </c>
       <c r="G762" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H762" t="inlineStr">
@@ -46957,7 +46965,7 @@
       </c>
       <c r="G763" t="inlineStr">
         <is>
-          <t>BASE INFANTERIA DE MARINA CONCON</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H763" t="inlineStr">
@@ -47323,7 +47331,7 @@
       </c>
       <c r="G769" t="inlineStr">
         <is>
-          <t>Servicio de Educación Pública Santa Corina</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H769" t="inlineStr">
@@ -47567,7 +47575,7 @@
       </c>
       <c r="G773" t="inlineStr">
         <is>
-          <t>Servicio de Educación Pública Santa Corina</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H773" t="inlineStr">
@@ -47628,7 +47636,7 @@
       </c>
       <c r="G774" t="inlineStr">
         <is>
-          <t>Servicio de Educación Pública Santa Corina</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H774" t="inlineStr">
@@ -47689,7 +47697,7 @@
       </c>
       <c r="G775" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H775" t="inlineStr">
@@ -47872,7 +47880,7 @@
       </c>
       <c r="G778" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H778" t="inlineStr">
@@ -47994,7 +48002,7 @@
       </c>
       <c r="G780" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H780" t="inlineStr">
@@ -48543,7 +48551,7 @@
       </c>
       <c r="G789" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H789" t="inlineStr">
@@ -48604,7 +48612,7 @@
       </c>
       <c r="G790" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Coyhaique" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H790" t="inlineStr">
@@ -48787,7 +48795,7 @@
       </c>
       <c r="G793" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H793" t="inlineStr">
@@ -48848,7 +48856,7 @@
       </c>
       <c r="G794" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H794" t="inlineStr">
@@ -48909,7 +48917,7 @@
       </c>
       <c r="G795" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Coyhaique" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H795" t="inlineStr">
@@ -49700,7 +49708,11 @@
           <t>61.980.840-1</t>
         </is>
       </c>
-      <c r="G808" t="inlineStr"/>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
       <c r="H808" t="inlineStr">
         <is>
           <t>Aysén</t>
@@ -49759,7 +49771,7 @@
       </c>
       <c r="G809" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H809" t="inlineStr">
@@ -49820,7 +49832,7 @@
       </c>
       <c r="G810" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H810" t="inlineStr">
@@ -49881,7 +49893,7 @@
       </c>
       <c r="G811" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Colina 1</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H811" t="inlineStr">
@@ -49942,7 +49954,7 @@
       </c>
       <c r="G812" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H812" t="inlineStr">
@@ -50186,7 +50198,7 @@
       </c>
       <c r="G816" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>Departamento de Salud Parral</t>
         </is>
       </c>
       <c r="H816" t="inlineStr">
@@ -50247,7 +50259,7 @@
       </c>
       <c r="G817" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H817" t="inlineStr">
@@ -50430,12 +50442,12 @@
       </c>
       <c r="G820" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Protección</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I820" t="inlineStr">
@@ -50491,7 +50503,7 @@
       </c>
       <c r="G821" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H821" t="inlineStr">
@@ -50674,7 +50686,7 @@
       </c>
       <c r="G824" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Río Negro - Educación</t>
+          <t>I MUNICIPALIDAD DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H824" t="inlineStr">
@@ -50735,7 +50747,7 @@
       </c>
       <c r="G825" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H825" t="inlineStr">
@@ -50796,7 +50808,7 @@
       </c>
       <c r="G826" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Concepción" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H826" t="inlineStr">
@@ -50918,7 +50930,7 @@
       </c>
       <c r="G828" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE EDUCACION,SALUD,CULTURA Y</t>
+          <t>CORPORACION MUNICIPAL DE EDUCACION,SALUD,CULTURA Y ATENCION AL MENOR,</t>
         </is>
       </c>
       <c r="H828" t="inlineStr">
@@ -51284,7 +51296,7 @@
       </c>
       <c r="G834" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H834" t="inlineStr">
@@ -51406,7 +51418,7 @@
       </c>
       <c r="G836" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H836" t="inlineStr">
@@ -51467,7 +51479,7 @@
       </c>
       <c r="G837" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H837" t="inlineStr">
@@ -51528,7 +51540,7 @@
       </c>
       <c r="G838" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H838" t="inlineStr">
@@ -51650,7 +51662,7 @@
       </c>
       <c r="G840" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H840" t="inlineStr">
@@ -52077,7 +52089,7 @@
       </c>
       <c r="G847" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H847" t="inlineStr">
@@ -52138,7 +52150,7 @@
       </c>
       <c r="G848" t="inlineStr">
         <is>
-          <t>BASE INFANTERIA DE MARINA TUMBES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H848" t="inlineStr">
@@ -52199,7 +52211,7 @@
       </c>
       <c r="G849" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H849" t="inlineStr">
@@ -52260,7 +52272,7 @@
       </c>
       <c r="G850" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H850" t="inlineStr">
@@ -52321,7 +52333,7 @@
       </c>
       <c r="G851" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H851" t="inlineStr">
@@ -52382,7 +52394,7 @@
       </c>
       <c r="G852" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H852" t="inlineStr">
@@ -52443,7 +52455,7 @@
       </c>
       <c r="G853" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H853" t="inlineStr">
@@ -52504,7 +52516,7 @@
       </c>
       <c r="G854" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H854" t="inlineStr">
@@ -52687,7 +52699,7 @@
       </c>
       <c r="G857" t="inlineStr">
         <is>
-          <t>BASE INFANTERIA DE MARINA TUMBES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H857" t="inlineStr">
@@ -52931,7 +52943,7 @@
       </c>
       <c r="G861" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H861" t="inlineStr">
@@ -53175,7 +53187,7 @@
       </c>
       <c r="G865" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H865" t="inlineStr">
@@ -53297,7 +53309,7 @@
       </c>
       <c r="G867" t="inlineStr">
         <is>
-          <t>Dirección General de Aeronáutica Civil</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H867" t="inlineStr">
@@ -53358,7 +53370,7 @@
       </c>
       <c r="G868" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H868" t="inlineStr">
@@ -53663,7 +53675,7 @@
       </c>
       <c r="G873" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H873" t="inlineStr">
@@ -53785,7 +53797,7 @@
       </c>
       <c r="G875" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H875" t="inlineStr">
@@ -53846,7 +53858,7 @@
       </c>
       <c r="G876" t="inlineStr">
         <is>
-          <t>BASE NAVAL PUERTO MONTT</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H876" t="inlineStr">
@@ -53968,7 +53980,7 @@
       </c>
       <c r="G878" t="inlineStr">
         <is>
-          <t>DIRECCION DE SEGURIDAD Y OPERACIONES MARITIMAS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H878" t="inlineStr">
@@ -54090,7 +54102,7 @@
       </c>
       <c r="G880" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H880" t="inlineStr">
@@ -54273,7 +54285,7 @@
       </c>
       <c r="G883" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepción</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H883" t="inlineStr">
@@ -54700,7 +54712,7 @@
       </c>
       <c r="G890" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H890" t="inlineStr">
@@ -54761,7 +54773,7 @@
       </c>
       <c r="G891" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H891" t="inlineStr">
@@ -54944,7 +54956,7 @@
       </c>
       <c r="G894" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo CCP Nueva Imperial</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H894" t="inlineStr">
@@ -55249,7 +55261,7 @@
       </c>
       <c r="G899" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H899" t="inlineStr">
@@ -55615,7 +55627,7 @@
       </c>
       <c r="G905" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H905" t="inlineStr">
@@ -55737,7 +55749,7 @@
       </c>
       <c r="G907" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo CDP Curacautín</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H907" t="inlineStr">
@@ -55859,7 +55871,7 @@
       </c>
       <c r="G909" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H909" t="inlineStr">
@@ -55981,7 +55993,7 @@
       </c>
       <c r="G911" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H911" t="inlineStr">
@@ -56408,7 +56420,7 @@
       </c>
       <c r="G918" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H918" t="inlineStr">
@@ -56530,7 +56542,7 @@
       </c>
       <c r="G920" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H920" t="inlineStr">
@@ -56652,7 +56664,7 @@
       </c>
       <c r="G922" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H922" t="inlineStr">
@@ -56713,7 +56725,7 @@
       </c>
       <c r="G923" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H923" t="inlineStr">
@@ -56774,7 +56786,7 @@
       </c>
       <c r="G924" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H924" t="inlineStr">
@@ -56835,7 +56847,7 @@
       </c>
       <c r="G925" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H925" t="inlineStr">
@@ -56896,7 +56908,7 @@
       </c>
       <c r="G926" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H926" t="inlineStr">
@@ -56957,7 +56969,7 @@
       </c>
       <c r="G927" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE COQUIMBO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H927" t="inlineStr">
@@ -57018,7 +57030,7 @@
       </c>
       <c r="G928" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H928" t="inlineStr">
@@ -57262,7 +57274,7 @@
       </c>
       <c r="G932" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H932" t="inlineStr">
@@ -57323,7 +57335,7 @@
       </c>
       <c r="G933" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H933" t="inlineStr">
@@ -57445,7 +57457,7 @@
       </c>
       <c r="G935" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H935" t="inlineStr">
@@ -57567,7 +57579,7 @@
       </c>
       <c r="G937" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H937" t="inlineStr">
@@ -57628,7 +57640,7 @@
       </c>
       <c r="G938" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H938" t="inlineStr">
@@ -57689,7 +57701,7 @@
       </c>
       <c r="G939" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H939" t="inlineStr">
@@ -57811,7 +57823,7 @@
       </c>
       <c r="G941" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H941" t="inlineStr">
@@ -57933,7 +57945,7 @@
       </c>
       <c r="G943" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmeria</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H943" t="inlineStr">
@@ -58055,7 +58067,7 @@
       </c>
       <c r="G945" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LUMACO</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H945" t="inlineStr">
@@ -58421,7 +58433,7 @@
       </c>
       <c r="G951" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmeria</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H951" t="inlineStr">
@@ -58482,7 +58494,7 @@
       </c>
       <c r="G952" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H952" t="inlineStr">
@@ -58543,7 +58555,7 @@
       </c>
       <c r="G953" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H953" t="inlineStr">
@@ -58665,7 +58677,7 @@
       </c>
       <c r="G955" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H955" t="inlineStr">
@@ -58848,7 +58860,7 @@
       </c>
       <c r="G958" t="inlineStr">
         <is>
-          <t>Juzgado de Letras y Familia de Villarrica</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H958" t="inlineStr">
@@ -58909,7 +58921,7 @@
       </c>
       <c r="G959" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H959" t="inlineStr">
@@ -58970,7 +58982,7 @@
       </c>
       <c r="G960" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - IX Zona Araucania</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H960" t="inlineStr">
@@ -59092,7 +59104,7 @@
       </c>
       <c r="G962" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H962" t="inlineStr">
@@ -59214,7 +59226,7 @@
       </c>
       <c r="G964" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H964" t="inlineStr">
@@ -59336,7 +59348,7 @@
       </c>
       <c r="G966" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H966" t="inlineStr">
@@ -59458,7 +59470,7 @@
       </c>
       <c r="G968" t="inlineStr">
         <is>
-          <t>Departamento De Educacion Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
         </is>
       </c>
       <c r="H968" t="inlineStr">
@@ -59519,7 +59531,7 @@
       </c>
       <c r="G969" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social Lampa</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H969" t="inlineStr">
@@ -59580,7 +59592,7 @@
       </c>
       <c r="G970" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social Lampa</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H970" t="inlineStr">
@@ -59707,7 +59719,7 @@
       </c>
       <c r="H972" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I972" t="inlineStr">
@@ -59763,7 +59775,7 @@
       </c>
       <c r="G973" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social Lampa</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H973" t="inlineStr">
@@ -59824,7 +59836,7 @@
       </c>
       <c r="G974" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H974" t="inlineStr">
@@ -60007,7 +60019,7 @@
       </c>
       <c r="G977" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H977" t="inlineStr">
@@ -60129,7 +60141,7 @@
       </c>
       <c r="G979" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE ANTOFAGASTA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H979" t="inlineStr">
@@ -60739,7 +60751,7 @@
       </c>
       <c r="G989" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H989" t="inlineStr">
@@ -60800,7 +60812,7 @@
       </c>
       <c r="G990" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del CDP Talagante</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H990" t="inlineStr">
@@ -60861,7 +60873,7 @@
       </c>
       <c r="G991" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H991" t="inlineStr">
@@ -60983,7 +60995,7 @@
       </c>
       <c r="G993" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H993" t="inlineStr">
@@ -61166,7 +61178,7 @@
       </c>
       <c r="G996" t="inlineStr">
         <is>
-          <t>Centro Educación y Trabajo Femenino Semiabierto St</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H996" t="inlineStr">
@@ -61227,7 +61239,7 @@
       </c>
       <c r="G997" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H997" t="inlineStr">
@@ -61349,7 +61361,7 @@
       </c>
       <c r="G999" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H999" t="inlineStr">
@@ -61837,7 +61849,7 @@
       </c>
       <c r="G1007" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE TALCAHUANO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H1007" t="inlineStr">
@@ -61898,7 +61910,7 @@
       </c>
       <c r="G1008" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE TALCAHUANO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H1008" t="inlineStr">
@@ -61959,7 +61971,7 @@
       </c>
       <c r="G1009" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE TALCAHUANO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H1009" t="inlineStr">
@@ -62020,7 +62032,7 @@
       </c>
       <c r="G1010" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H1010" t="inlineStr">
@@ -62081,7 +62093,7 @@
       </c>
       <c r="G1011" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H1011" t="inlineStr">
@@ -62203,7 +62215,7 @@
       </c>
       <c r="G1013" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H1013" t="inlineStr">
@@ -62264,7 +62276,7 @@
       </c>
       <c r="G1014" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H1014" t="inlineStr">
@@ -62508,7 +62520,7 @@
       </c>
       <c r="G1018" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Menores</t>
+          <t>SERVICIO NACIONAL DE MENORES</t>
         </is>
       </c>
       <c r="H1018" t="inlineStr">
@@ -62813,7 +62825,7 @@
       </c>
       <c r="G1023" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H1023" t="inlineStr">
@@ -62874,7 +62886,7 @@
       </c>
       <c r="G1024" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1024" t="inlineStr">
@@ -62996,7 +63008,7 @@
       </c>
       <c r="G1026" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H1026" t="inlineStr">
@@ -63240,7 +63252,7 @@
       </c>
       <c r="G1030" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1030" t="inlineStr">
@@ -63423,7 +63435,7 @@
       </c>
       <c r="G1033" t="inlineStr">
         <is>
-          <t>Departamento Comunal de Salud</t>
+          <t>I MUNICIPALIDAD DE TUCAPEL</t>
         </is>
       </c>
       <c r="H1033" t="inlineStr">
@@ -63545,7 +63557,7 @@
       </c>
       <c r="G1035" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Menores</t>
+          <t>SERVICIO NACIONAL DE MENORES</t>
         </is>
       </c>
       <c r="H1035" t="inlineStr">
@@ -63606,7 +63618,7 @@
       </c>
       <c r="G1036" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1036" t="inlineStr">
@@ -63667,7 +63679,7 @@
       </c>
       <c r="G1037" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Colina 1</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1037" t="inlineStr">
@@ -64033,7 +64045,7 @@
       </c>
       <c r="G1043" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA Va ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H1043" t="inlineStr">
@@ -64216,7 +64228,7 @@
       </c>
       <c r="G1046" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H1046" t="inlineStr">
@@ -64399,7 +64411,7 @@
       </c>
       <c r="G1049" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H1049" t="inlineStr">
@@ -64460,7 +64472,7 @@
       </c>
       <c r="G1050" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H1050" t="inlineStr">
@@ -64521,7 +64533,7 @@
       </c>
       <c r="G1051" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H1051" t="inlineStr">
@@ -64643,7 +64655,7 @@
       </c>
       <c r="G1053" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1053" t="inlineStr">
@@ -64887,7 +64899,7 @@
       </c>
       <c r="G1057" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H1057" t="inlineStr">
@@ -64948,7 +64960,7 @@
       </c>
       <c r="G1058" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H1058" t="inlineStr">
@@ -65009,7 +65021,7 @@
       </c>
       <c r="G1059" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1059" t="inlineStr">
@@ -65131,7 +65143,7 @@
       </c>
       <c r="G1061" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1061" t="inlineStr">
@@ -65192,7 +65204,7 @@
       </c>
       <c r="G1062" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1062" t="inlineStr">
@@ -65253,7 +65265,7 @@
       </c>
       <c r="G1063" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H1063" t="inlineStr">
@@ -65314,7 +65326,7 @@
       </c>
       <c r="G1064" t="inlineStr">
         <is>
-          <t>Ejército de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H1064" t="inlineStr">
@@ -65436,7 +65448,7 @@
       </c>
       <c r="G1066" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1066" t="inlineStr">
@@ -65609,7 +65621,7 @@
       </c>
       <c r="E1069" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1069" t="inlineStr">
@@ -65924,7 +65936,7 @@
       </c>
       <c r="G1074" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1074" t="inlineStr">
@@ -66046,7 +66058,7 @@
       </c>
       <c r="G1076" t="inlineStr">
         <is>
-          <t>JEFATURA DE BIENESTAR (I.P)</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H1076" t="inlineStr">
@@ -66107,7 +66119,7 @@
       </c>
       <c r="G1077" t="inlineStr">
         <is>
-          <t>Dirección de Administración de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H1077" t="inlineStr">
@@ -66351,7 +66363,7 @@
       </c>
       <c r="G1081" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1081" t="inlineStr">
@@ -66595,7 +66607,7 @@
       </c>
       <c r="G1085" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1085" t="inlineStr">
@@ -66656,7 +66668,7 @@
       </c>
       <c r="G1086" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H1086" t="inlineStr">
@@ -66900,7 +66912,7 @@
       </c>
       <c r="G1090" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H1090" t="inlineStr">
@@ -67144,7 +67156,7 @@
       </c>
       <c r="G1094" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1094" t="inlineStr">
@@ -67266,7 +67278,7 @@
       </c>
       <c r="G1096" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H1096" t="inlineStr">
@@ -67571,7 +67583,7 @@
       </c>
       <c r="G1101" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo CDP Curacautín</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1101" t="inlineStr">
@@ -67632,7 +67644,7 @@
       </c>
       <c r="G1102" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1102" t="inlineStr">
@@ -67693,7 +67705,7 @@
       </c>
       <c r="G1103" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1103" t="inlineStr">
@@ -67754,7 +67766,7 @@
       </c>
       <c r="G1104" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H1104" t="inlineStr">
@@ -67876,7 +67888,7 @@
       </c>
       <c r="G1106" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H1106" t="inlineStr">
@@ -67998,7 +68010,7 @@
       </c>
       <c r="G1108" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H1108" t="inlineStr">
